--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,7 +687,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>کد بازبینی + host test</t>
@@ -698,7 +697,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -761,7 +759,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
@@ -772,7 +769,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -835,7 +831,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
@@ -846,7 +841,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -909,7 +903,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
@@ -920,7 +913,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -983,14 +975,11 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1053,14 +1042,11 @@
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1123,7 +1109,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>check_ai_rules.sh</t>
@@ -1134,7 +1119,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1197,7 +1181,6 @@
           <t>قبول</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>check_ai_rules.sh</t>
@@ -1208,7 +1191,6 @@
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1271,14 +1253,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1341,17 +1320,86 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RT-011</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>تبدیل تیک به ms در چک‌این‌های IWDG</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>کد</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>هر ۷ محل CheckIn/PollKick واچ‌داگ در پنج تسک را بگرد: همه باید زمان را از تبدیل rtos_time بگیرند (func__Rtos_TicksToMilliseconds)، نه تیک خام کرنل</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>در فرکانس تیک ۱۰۰۰ هرتز رفتار دقیقاً مثل قبل؛ اگر روزی فرکانس تیک عوض شود، مهلت‌های واچ‌داگ خودکار بر حسب ms درست می‌مانند</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>هیچ چک‌اینی تیک خام را جای ms ندهد؛ هر دو گیت سبز</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: هر دو گیت سبز، بودجهٔ RAM/فلش بدون تغییر؛ تست برد: در انتظار</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>004fbf1</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -654,7 +654,10 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>task_control را اجرا کن و snapshot را قبل از GetSnapshot چک کن</t>
+          <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بوت کن (یا ADC را نگه دار تا snapshot نیاید).
+گام ۲: task_control را اجرا کن و snapshot را درست قبل از GetSnapshot بخوان.
+گام ۳: هر 9 فیلد باید صفر باشد: v_in=0، v_bat24=0، v_bat12=0، v_low=0، v_high=0، i1=0، i2=0، input_present=false و valid=false.
+گام ۴: هیچ فیلدی نباید زبالهٔ پشته باشد؛ همین رفتار را در task_comm، task_ui و task_protection هم باید ببینی.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -726,7 +729,9 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>task_comm را اجرا کن</t>
+          <t>گام ۱: برد را با measurement خاموش بوت کن.
+گام ۲: task_comm را اجرا کن و snapshot را قبل از GetSnapshot بخوان (3 ثانیه).
+گام ۳: هر 9 فیلد باید از قبل صفر شده باشد؛ هیچ فیلد نامشخص (indeterminate) نباید در ساختار باشد.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -798,7 +803,9 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>task_ui را اجرا کن</t>
+          <t>گام ۱: برد را با measurement خاموش بوت کن.
+گام ۲: task_ui را اجرا کن (3 ثانیه).
+گام ۳: هر 9 فیلد snapshot باید صفر باشد و خروجی UI باید safe-off باشد؛ یعنی همهٔ LEDها خاموش بمانند.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -870,7 +877,9 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>task_protection را اجرا کن</t>
+          <t>گام ۱: برد را با measurement خاموش بوت کن.
+گام ۲: task_protection را اجرا کن (3 ثانیه).
+گام ۳: هر 9 فیلد باید صفر باشد و Protection فقط valid را چک کند؛ هیچ fault کاذبی نباید ساخته شود.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -942,7 +951,10 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>یک پاس کامل control را لاگ کن</t>
+          <t>گام ۱: لینک و شارژر را فعال کن تا یک پاس واقعی control اجرا شود.
+گام ۲: یک پاس کامل task_control را با لاگ یا نقطه‌توقف (breakpoint) قدم‌به‌قدم دنبال کن.
+گام ۳: ترتیب اجرا باید دقیقاً این باشد: اول imbalance، بعد fault، بعد خطای فنی شارژر، بعد mcu_power_path، بعد changeover، بعد ارزیابی شارژر و در آخر poll واچ‌داگ.
+گام ۴: پاس باید در همان 10 میلی‌ثانیه تمام شود و ترتیب در همهٔ پاس‌ها حفظ شود.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1009,7 +1021,10 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IWDG را با لاگ check-in ببین</t>
+          <t>گام ۱: همهٔ تسک‌ها را فعال کن و لاگ check-in واچ‌داگ را باز کن.
+گام ۲: 5 ثانیه نگاه کن: فقط task_control کیک (kick) می‌زند؛ بقیهٔ تسک‌ها فقط check-in می‌کنند.
+گام ۳: یکی از تسک‌ها را عمداً stale کن (توقفش بده).
+گام ۴: از آن لحظه نباید دیگر kick زده شود؛ kick فقط وقتی مجاز است که همهٔ تسک‌ها تازه باشند.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1076,7 +1091,9 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>grep HAL_Delay در کل Firmware</t>
+          <t>گام ۱: در کل پوشهٔ Firmware دنبال HAL_Delay بگرد (grep).
+گام ۲: باید صفر مورد پیدا شود.
+گام ۳: هر تأخیری در کد باید فقط از Rtos_DelayMilliseconds یا osDelayUntil باشد.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1148,7 +1165,10 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rtos_app.c و rtos_config.h را چک کن</t>
+          <t>گام ۱: فایل‌های rtos_app.c و rtos_config.h را باز کن.
+گام ۲: برای تک‌تک threadها چک کن که با حافظهٔ ثابت ساخته شده‌اند (cb_mem و stack_mem).
+گام ۳: دنبال malloc و free در کد محصول بگرد؛ نباید هیچ‌کدام باشد و heap_4 هم نباید لینک شده باشد.
+گام ۴: نتیجه: فقط تخصیص استاتیک مجاز است.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1220,7 +1240,10 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>از پنل یک confirm بساز (قطع PWM)</t>
+          <t>گام ۱: پنل را وصل کن.
+گام ۲: یک دیالوگ تأیید بساز (مثلاً دکمهٔ قطع PWM را بزن).
+گام ۳: دیالوگ باید تیره (#pmod) باشد و متنش بگوید Enter تأیید و Esc انصراف است.
+گام ۴: یک بار Enter بزن (تأیید کند) و یک بار در دفعهٔ بعد Esc (لغو کند)؛ هر دو باید کار کنند.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1287,7 +1310,10 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>دو confirm پشت سر هم</t>
+          <t>گام ۱: پنل را وصل کن.
+گام ۲: دو دیالوگ تأیید پشت سر هم بساز (دو درخواست نزدیک به هم).
+گام ۳: 5 ثانیه نگاه کن: دیالوگ‌ها باید یکی‌یکی و به نوبت (Promise queue) بیایند.
+گام ۴: هیچ‌وقت دو دیالوگ نباید روی هم بیفتند.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1354,7 +1380,10 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>هر ۷ محل CheckIn/PollKick واچ‌داگ در پنج تسک را بگرد: همه باید زمان را از تبدیل rtos_time بگیرند (func__Rtos_TicksToMilliseconds)، نه تیک خام کرنل</t>
+          <t>گام ۱: هر 7 محل check-in و poll واچ‌داگ را در پنج تسک پیدا کن (task_control، task_comm، task_measurement، task_protection و task_ui).
+گام ۲: در هر محل چک کن زمان از تبدیل func__Rtos_TicksToMilliseconds(osKernelGetTickCount()) گذشته باشد، نه تیک خام کرنل.
+گام ۳: با فرکانس تیک فعلی (1000 هرتز) رفتار باید دقیقاً مثل قبل باشد و هر دو گیت (check_ai_rules و check_firmware_syntax) سبز شوند.
+گام ۴ (برد): روی برد واقعی واچ‌داگ را زیر نظر بگیر؛ اگر روزی فرکانس تیک عوض شود، مهلت‌ها خودکار بر حسب میلی‌ثانیه درست می‌مانند. تست برد هنوز در انتظار است.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">

--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -15,15 +15,20 @@
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,16 +36,90 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +127,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,6 +555,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -423,93 +563,100 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Rtos — تسک‌ها، snapshot zeroing، watchdog، ترتیب اجرا</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>هدف: اثبات اینکه تسک‌های CMSIS-RTOS2 ساده، خوانا، بدون HAL_Delay، با تخصیص استاتیک و zero کردن کامل snapshot کار می‌کنند</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>قوانین: هر تست باید پیش‌شرط، ورودی، انتظار، معیار قبولی صریح داشته باشد؛ نتیجه واقعی فقط با اندازه‌گیری روی برد</t>
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>نسخه</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>شرح تغییر</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>ایجاد اولیه Rtos_Validation — snapshot zeroing task_control (CO-023)، watchdog poll، ترتیب imbalance-&gt;fault-&gt;changeover-&gt;charger، static allocation</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>9cb64eb</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>اضافه شدن RT-008..RT-010 برای panel dialog و Enter/Esc</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -517,142 +664,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Rtos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>RT-001</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>snapshot zeroing task_control</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>برد با MODULE_MEASUREMENT=0 یا ADC نگه‌داشته</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بوت کن (یا ADC را نگه دار تا snapshot نیاید).
 گام ۲: task_control را اجرا کن و snapshot را درست قبل از GetSnapshot بخوان.
@@ -660,296 +827,308 @@
 گام ۴: هیچ فیلدی نباید زبالهٔ پشته باشد؛ همین رفتار را در task_comm، task_ui و task_protection هم باید ببینی.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>هر 9 فیلد snapshot صفر: v_in=0 v_bat24=0 v_bat12=0 v_low=0 v_high=0 i1=0 i2=0 input_present=false valid=false</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>امن</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>بدون زباله پشته؛ مانند task_comm/task_ui/task_protection</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>کد بازبینی + host test</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="10" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>RT-002</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>snapshot zeroing task_comm</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>برد با measurement خاموش</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>گام ۱: برد را با measurement خاموش بوت کن.
 گام ۲: task_comm را اجرا کن و snapshot را قبل از GetSnapshot بخوان (3 ثانیه).
 گام ۳: هر 9 فیلد باید از قبل صفر شده باشد؛ هیچ فیلد نامشخص (indeterminate) نباید در ساختار باشد.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>هر 9 فیلد صفر شده قبل از GetSnapshot</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>بدون indeterminate struct</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="P6" s="13" t="n"/>
+      <c r="Q6" s="14" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>RT-003</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>snapshot zeroing task_ui</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>برد با measurement خاموش</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>گام ۱: برد را با measurement خاموش بوت کن.
 گام ۲: task_ui را اجرا کن (3 ثانیه).
 گام ۳: هر 9 فیلد snapshot باید صفر باشد و خروجی UI باید safe-off باشد؛ یعنی همهٔ LEDها خاموش بمانند.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>هر 9 فیلد صفر؛ UI safe-off</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>safe-off</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>LED خاموش</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="10" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="40.5" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>RT-004</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>snapshot zeroing task_protection</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>برد با measurement خاموش</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>گام ۱: برد را با measurement خاموش بوت کن.
 گام ۲: task_protection را اجرا کن (3 ثانیه).
 گام ۳: هر 9 فیلد باید صفر باشد و Protection فقط valid را چک کند؛ هیچ fault کاذبی نباید ساخته شود.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>هر 9 فیلد صفر؛ Protection فقط valid را چک کند</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>بدون fault کاذب</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" s="11" t="n"/>
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="14" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>RT-005</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>ترتیب اجرا در task_control</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>لینک فعال + شارژر فعال</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>گام ۱: لینک و شارژر را فعال کن تا یک پاس واقعی control اجرا شود.
 گام ۲: یک پاس کامل task_control را با لاگ یا نقطه‌توقف (breakpoint) قدم‌به‌قدم دنبال کن.
@@ -957,69 +1136,73 @@
 گام ۴: پاس باید در همان 10 میلی‌ثانیه تمام شود و ترتیب در همهٔ پاس‌ها حفظ شود.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>ترتیب ثابت: imbalance -&gt; fault -&gt; charger technical fault -&gt; mcu_power_path -&gt; changeover -&gt; charger evaluate -&gt; watchdog poll</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>ترتیب حفظ شود</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="15" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="8" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="10" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>RT-006</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>watchdog poll و check-in</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>همه تسک‌ها فعال</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>گام ۱: همهٔ تسک‌ها را فعال کن و لاگ check-in واچ‌داگ را باز کن.
 گام ۲: 5 ثانیه نگاه کن: فقط task_control کیک (kick) می‌زند؛ بقیهٔ تسک‌ها فقط check-in می‌کنند.
@@ -1027,143 +1210,150 @@
 گام ۴: از آن لحظه نباید دیگر kick زده شود؛ kick فقط وقتی مجاز است که همهٔ تسک‌ها تازه باشند.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>فقط task_control kick می‌زند؛ بقیه تسک‌ها check-in می‌کنند؛ اگر یک تسک stale شود kick انجام نشود</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>kick فقط وقتی همه تازه‌اند</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="15" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="M10" s="11" t="n"/>
+      <c r="N10" s="11" t="n"/>
+      <c r="O10" s="13" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="14" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="40.5" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>RT-007</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>بدون HAL_Delay</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>کد</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>گام ۱: در کل پوشهٔ Firmware دنبال HAL_Delay بگرد (grep).
 گام ۲: باید صفر مورد پیدا شود.
 گام ۳: هر تأخیری در کد باید فقط از Rtos_DelayMilliseconds یا osDelayUntil باشد.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>هیچ HAL_Delay وجود نداشته باشد؛ فقط Rtos_DelayMilliseconds و osDelayUntil</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>0 مورد HAL_Delay</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>check_ai_rules.sh</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="8" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="10" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>RT-008</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>تخصیص استاتیک</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>کد</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>گام ۱: فایل‌های rtos_app.c و rtos_config.h را باز کن.
 گام ۲: برای تک‌تک threadها چک کن که با حافظهٔ ثابت ساخته شده‌اند (cb_mem و stack_mem).
@@ -1171,74 +1361,77 @@
 گام ۴: نتیجه: فقط تخصیص استاتیک مجاز است.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>همه threadها با cb_mem و stack_mem ثابت؛ بدون malloc/free؛ heap_4 لینک نشود</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>static allocation + no malloc</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" s="11" t="n"/>
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="M12" s="11" t="n"/>
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>check_ai_rules.sh</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="13" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="P12" s="13" t="n"/>
+      <c r="Q12" s="14" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>RT-009</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>panel dialog Enter/Esc</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: یک دیالوگ تأیید بساز (مثلاً دکمهٔ قطع PWM را بزن).
@@ -1246,69 +1439,73 @@
 گام ۴: یک بار Enter بزن (تأیید کند) و یک بار در دفعهٔ بعد Esc (لغو کند)؛ هر دو باید کار کنند.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>کلیک قطع</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>دیالوگ تیره #pmod با متن Enter=تأیید Esc=انصراف؛ Enter تأیید و Esc لغو کند</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>Enter/Esc کار کند + استایل تیره</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="10" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>RT-010</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>panel dialog queue PMQ</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: دو دیالوگ تأیید پشت سر هم بساز (دو درخواست نزدیک به هم).
@@ -1316,69 +1513,73 @@
 گام ۴: هیچ‌وقت دو دیالوگ نباید روی هم بیفتند.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>دو درخواست</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>دیالوگ‌ها با Promise queue یکی‌یکی بیایند، نه روی هم</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>صف</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>بدون همپوشانی</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="16" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="M14" s="11" t="n"/>
+      <c r="N14" s="11" t="n"/>
+      <c r="O14" s="13" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="P14" s="13" t="n"/>
+      <c r="Q14" s="14" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>RT-011</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>تبدیل تیک به ms در چک‌این‌های IWDG</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>کد</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>گام ۱: هر 7 محل check-in و poll واچ‌داگ را در پنج تسک پیدا کن (task_control، task_comm، task_measurement، task_protection و task_ui).
 گام ۲: در هر محل چک کن زمان از تبدیل func__Rtos_TicksToMilliseconds(osKernelGetTickCount()) گذشته باشد، نه تیک خام کرنل.
@@ -1386,96 +1587,350 @@
 گام ۴ (برد): روی برد واقعی واچ‌داگ را زیر نظر بگیر؛ اگر روزی فرکانس تیک عوض شود، مهلت‌ها خودکار بر حسب میلی‌ثانیه درست می‌مانند. تست برد هنوز در انتظار است.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>در فرکانس تیک ۱۰۰۰ هرتز رفتار دقیقاً مثل قبل؛ اگر روزی فرکانس تیک عوض شود، مهلت‌های واچ‌داگ خودکار بر حسب ms درست می‌مانند</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>هیچ چک‌اینی تیک خام را جای ms ندهد؛ هر دو گیت سبز</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: هر دو گیت سبز، بودجهٔ RAM/فلش بدون تغییر؛ تست برد: در انتظار</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="15" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>004fbf1</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="Q16" s="17">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="17">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="17">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="17">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="17">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="17">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="17">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="17">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="17">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="17">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="17">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="17">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="17">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="17">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="17">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="17">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="17">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="17">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="17">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="17">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="17">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="17">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="17">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="17">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="17">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="17">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="17">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="17">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="17">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="17">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="17">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="17">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="17">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="17">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="17">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="Q51" s="17">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="Q52" s="17">
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="Q53" s="17">
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="Q54" s="17">
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="Q55" s="17">
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:Q15"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5:L95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$7:$A$12</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>مرجع سناریوهای Rtos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>task_control: snapshot zeroing مانند task_comm/task_ui/task_protection — هر 9 فیلد صفر قبل از GetSnapshot</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>task_control ترتیب: imbalance (prev state) -&gt; fault evaluate -&gt; jitter run -&gt; charger technical fault -&gt; mcu_power_path -&gt; imbalance evaluate -&gt; changeover evaluate -&gt; charger evaluate -&gt; watchdog poll</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>watchdog: BSP_IWDG_SLOT_* check-in در هر تسک؛ PollKick فقط در control</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>RTOS: CMSIS-RTOS2 با osDelayUntil و MillisecondsToTicks، بدون فرض tick=1ms</t>
         </is>
@@ -1489,97 +1944,102 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>شناسه ایراد</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>تاریخ ثبت</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>تاریخ رفع</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>commit رفع</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>BUG-RT-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>RT-001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>task_control فقط valid=false می‌کرد، 8 فیلد دیگر زباله پشته داشت — latent defect</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>رفع شد</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1587,6 +2047,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1594,21 +2055,23 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Rtos</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>این برگه پس از پر شدن ستون نتیجه واقعی در برنامه تست و رفع ایرادهای ثبت شده امضا می‌شود</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
@@ -1622,41 +2085,96 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>فهرست ثابت‌ها و آستانه‌های Rtos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TASK_STACK_* در rtos_config.h با واحد word — UI/MEASUREMENT/PROTECTION/CONTROL/COMM</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>APP_CONFIG.control_period_ms=10u protection=5u comm=100u</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>BSP_IWDG_STALE_MS و SLOT_* در bsp_iwdg.h</t>
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>رد</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>مسدود</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1664,6 +2182,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1671,42 +2190,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ماشین حالت Rtos — تسک‌ها</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>task_measurement: BspAdc_Init -&gt; Measurement_Init -&gt; retry Start هر 1s با check-in -&gt; loop osDelayUntil 1ms -&gt; Measurement_Run -&gt; check-in</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>task_control: Changeover_Init -&gt; McuPowerPath_Init -&gt; Charger_Init -&gt; Jitter_Init -&gt; Imbalance_Init -&gt; loop: snapshot zero -&gt; Fault_Evaluate -&gt; Jitter_Run -&gt; Charger_TechnicalFault -&gt; McuPowerPath_Run -&gt; Imbalance_Evaluate (prev state) -&gt; Changeover_Evaluate -&gt; Charger_Evaluate -&gt; PollKick -&gt; Delay</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>task_comm: EspLink_Init -&gt; loop: snapshot zero -&gt; Measurement_GetSnapshot -&gt; Fault_Get -&gt; EspLink_Run -&gt; check-in -&gt; Delay comm_period</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>task_ui: Ui_Init -&gt; BoardTest_Start -&gt; loop: snapshot zero -&gt; GetSnapshot -&gt; Ui_Tick -&gt; check-in -&gt; Delay UI_TICK_MS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>task_protection: loop: snapshot zero -&gt; GetSnapshot -&gt; Protection_Run -&gt; check-in -&gt; Delay protection_period</t>
         </is>

--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +82,17 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="8">
@@ -145,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -192,6 +206,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -654,8 +674,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" location="'تست‌های برنامه‌نویسی'!A8" r:id="rId1"/>
+    <hyperlink ref="C9" location="'تست‌های برنامه‌نویسی'!A11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -668,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -801,408 +821,25 @@
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>RT-001</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>snapshot zeroing task_control</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+          <t>RT-006</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>watchdog poll و check-in</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>برد با MODULE_MEASUREMENT=0 یا ADC نگه‌داشته</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بوت کن (یا ADC را نگه دار تا snapshot نیاید).
-گام ۲: task_control را اجرا کن و snapshot را درست قبل از GetSnapshot بخوان.
-گام ۳: هر 9 فیلد باید صفر باشد: v_in=0، v_bat24=0، v_bat12=0، v_low=0، v_high=0، i1=0، i2=0، input_present=false و valid=false.
-گام ۴: هیچ فیلدی نباید زبالهٔ پشته باشد؛ همین رفتار را در task_comm، task_ui و task_protection هم باید ببینی.</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>3s</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>هر 9 فیلد snapshot صفر: v_in=0 v_bat24=0 v_bat12=0 v_low=0 v_high=0 i1=0 i2=0 input_present=false valid=false</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>امن</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>بدون زباله پشته؛ مانند task_comm/task_ui/task_protection</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>قبول</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="n"/>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>کد بازبینی + host test</t>
-        </is>
-      </c>
-      <c r="O5" s="8" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P5" s="8" t="n"/>
-      <c r="Q5" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>RT-002</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>snapshot zeroing task_comm</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>برد با measurement خاموش</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>گام ۱: برد را با measurement خاموش بوت کن.
-گام ۲: task_comm را اجرا کن و snapshot را قبل از GetSnapshot بخوان (3 ثانیه).
-گام ۳: هر 9 فیلد باید از قبل صفر شده باشد؛ هیچ فیلد نامشخص (indeterminate) نباید در ساختار باشد.</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>3s</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>هر 9 فیلد صفر شده قبل از GetSnapshot</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>بدون indeterminate struct</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>قبول</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="n"/>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>کد بازبینی</t>
-        </is>
-      </c>
-      <c r="O6" s="13" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="14" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>RT-003</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>snapshot zeroing task_ui</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>برد با measurement خاموش</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>گام ۱: برد را با measurement خاموش بوت کن.
-گام ۲: task_ui را اجرا کن (3 ثانیه).
-گام ۳: هر 9 فیلد snapshot باید صفر باشد و خروجی UI باید safe-off باشد؛ یعنی همهٔ LEDها خاموش بمانند.</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>3s</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>هر 9 فیلد صفر؛ UI safe-off</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>safe-off</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>LED خاموش</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>قبول</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>کد بازبینی</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="n"/>
-      <c r="Q7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40.5" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>RT-004</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>snapshot zeroing task_protection</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>برد با measurement خاموش</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>گام ۱: برد را با measurement خاموش بوت کن.
-گام ۲: task_protection را اجرا کن (3 ثانیه).
-گام ۳: هر 9 فیلد باید صفر باشد و Protection فقط valid را چک کند؛ هیچ fault کاذبی نباید ساخته شود.</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>3s</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>هر 9 فیلد صفر؛ Protection فقط valid را چک کند</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>بدون fault کاذب</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>قبول</t>
-        </is>
-      </c>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>کد بازبینی</t>
-        </is>
-      </c>
-      <c r="O8" s="13" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="14" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>RT-005</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>ترتیب اجرا در task_control</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>لینک فعال + شارژر فعال</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>گام ۱: لینک و شارژر را فعال کن تا یک پاس واقعی control اجرا شود.
-گام ۲: یک پاس کامل task_control را با لاگ یا نقطه‌توقف (breakpoint) قدم‌به‌قدم دنبال کن.
-گام ۳: ترتیب اجرا باید دقیقاً این باشد: اول imbalance، بعد fault، بعد خطای فنی شارژر، بعد mcu_power_path، بعد changeover، بعد ارزیابی شارژر و در آخر poll واچ‌داگ.
-گام ۴: پاس باید در همان 10 میلی‌ثانیه تمام شود و ترتیب در همهٔ پاس‌ها حفظ شود.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>10ms</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>ترتیب ثابت: imbalance -&gt; fault -&gt; charger technical fault -&gt; mcu_power_path -&gt; changeover -&gt; charger evaluate -&gt; watchdog poll</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>ترتیب حفظ شود</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="15" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="8" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P9" s="8" t="n"/>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>RT-006</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>watchdog poll و check-in</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>همه تسک‌ها فعال</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>گام ۱: همهٔ تسک‌ها را فعال کن و لاگ check-in واچ‌داگ را باز کن.
 گام ۲: 5 ثانیه نگاه کن: فقط task_control کیک (kick) می‌زند؛ بقیهٔ تسک‌ها فقط check-in می‌کنند.
@@ -1210,228 +847,73 @@
 گام ۴: از آن لحظه نباید دیگر kick زده شود؛ kick فقط وقتی مجاز است که همهٔ تسک‌ها تازه باشند.</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>فقط task_control kick می‌زند؛ بقیه تسک‌ها check-in می‌کنند؛ اگر یک تسک stale شود kick انجام نشود</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>kick فقط وقتی همه تازه‌اند</t>
         </is>
       </c>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="15" t="inlineStr">
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="15" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="11" t="n"/>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="13" t="inlineStr">
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="14" t="inlineStr">
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40.5" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>RT-007</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>بدون HAL_Delay</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>کد</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>گام ۱: در کل پوشهٔ Firmware دنبال HAL_Delay بگرد (grep).
-گام ۲: باید صفر مورد پیدا شود.
-گام ۳: هر تأخیری در کد باید فقط از Rtos_DelayMilliseconds یا osDelayUntil باشد.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>1s</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>هیچ HAL_Delay وجود نداشته باشد؛ فقط Rtos_DelayMilliseconds و osDelayUntil</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>0 مورد HAL_Delay</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>قبول</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>check_ai_rules.sh</t>
-        </is>
-      </c>
-      <c r="O11" s="8" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P11" s="8" t="n"/>
-      <c r="Q11" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>RT-008</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>تخصیص استاتیک</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>کد</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>گام ۱: فایل‌های rtos_app.c و rtos_config.h را باز کن.
-گام ۲: برای تک‌تک threadها چک کن که با حافظهٔ ثابت ساخته شده‌اند (cb_mem و stack_mem).
-گام ۳: دنبال malloc و free در کد محصول بگرد؛ نباید هیچ‌کدام باشد و heap_4 هم نباید لینک شده باشد.
-گام ۴: نتیجه: فقط تخصیص استاتیک مجاز است.</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>1s</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>همه threadها با cb_mem و stack_mem ثابت؛ بدون malloc/free؛ heap_4 لینک نشود</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>static allocation + no malloc</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>قبول</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="n"/>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>check_ai_rules.sh</t>
-        </is>
-      </c>
-      <c r="O12" s="13" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="14" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>RT-009</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>panel dialog Enter/Esc</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: یک دیالوگ تأیید بساز (مثلاً دکمهٔ قطع PWM را بزن).
@@ -1439,73 +921,73 @@
 گام ۴: یک بار Enter بزن (تأیید کند) و یک بار در دفعهٔ بعد Esc (لغو کند)؛ هر دو باید کار کنند.</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>کلیک قطع</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>دیالوگ تیره #pmod با متن Enter=تأیید Esc=انصراف؛ Enter تأیید و Esc لغو کند</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Enter/Esc کار کند + استایل تیره</t>
         </is>
       </c>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M13" s="6" t="n"/>
-      <c r="N13" s="6" t="n"/>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P13" s="8" t="n"/>
-      <c r="Q13" s="10" t="inlineStr">
+      <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="10" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>RT-010</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>panel dialog queue PMQ</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>پنل وصل</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>گام ۱: پنل را وصل کن.
 گام ۲: دو دیالوگ تأیید پشت سر هم بساز (دو درخواست نزدیک به هم).
@@ -1513,385 +995,1183 @@
 گام ۴: هیچ‌وقت دو دیالوگ نباید روی هم بیفتند.</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>دو درخواست</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>دیالوگ‌ها با Promise queue یکی‌یکی بیایند، نه روی هم</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>صف</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>بدون همپوشانی</t>
         </is>
       </c>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M14" s="11" t="n"/>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="13" t="inlineStr">
+      <c r="M7" s="11" t="n"/>
+      <c r="N7" s="11" t="n"/>
+      <c r="O7" s="13" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="14" t="inlineStr">
+      <c r="P7" s="13" t="n"/>
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
+    <row r="8" ht="40.5" customHeight="1">
+      <c r="Q8" s="17">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="Q9" s="17">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="Q10" s="17">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="40.5" customHeight="1">
+      <c r="Q11" s="17">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="Q12" s="17">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="Q13" s="17">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="Q14" s="17">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>RT-011</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>تبدیل تیک به ms در چک‌این‌های IWDG</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>کد</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>گام ۱: هر 7 محل check-in و poll واچ‌داگ را در پنج تسک پیدا کن (task_control، task_comm، task_measurement، task_protection و task_ui).
-گام ۲: در هر محل چک کن زمان از تبدیل func__Rtos_TicksToMilliseconds(osKernelGetTickCount()) گذشته باشد، نه تیک خام کرنل.
-گام ۳: با فرکانس تیک فعلی (1000 هرتز) رفتار باید دقیقاً مثل قبل باشد و هر دو گیت (check_ai_rules و check_firmware_syntax) سبز شوند.
-گام ۴ (برد): روی برد واقعی واچ‌داگ را زیر نظر بگیر؛ اگر روزی فرکانس تیک عوض شود، مهلت‌ها خودکار بر حسب میلی‌ثانیه درست می‌مانند. تست برد هنوز در انتظار است.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>در فرکانس تیک ۱۰۰۰ هرتز رفتار دقیقاً مثل قبل؛ اگر روزی فرکانس تیک عوض شود، مهلت‌های واچ‌داگ خودکار بر حسب ms درست می‌مانند</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>هیچ چک‌اینی تیک خام را جای ms ندهد؛ هر دو گیت سبز</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>هاست 2026-10-15: هر دو گیت سبز، بودجهٔ RAM/فلش بدون تغییر؛ تست برد: در انتظار</t>
-        </is>
-      </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>004fbf1</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="n"/>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
+      <c r="Q15" s="17">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="Q16" s="17">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="Q17" s="17">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="Q18" s="17">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="Q19" s="17">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="Q20" s="17">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="Q21" s="17">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="Q22" s="17">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="17">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="17">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="17">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="17">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="17">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="17">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="17">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="17">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="17">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="17">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="17">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="17">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="17">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="17">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="17">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="17">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="17">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="17">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="17">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="17">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="17">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="17">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="17">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="17">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="17">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="Q48" s="17">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="Q49" s="17">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="Q50" s="17">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="Q51" s="17">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="Q52" s="17">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="Q53" s="17">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="Q54" s="17">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="Q55" s="17">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q15"/>
+  <autoFilter ref="A4:Q47"/>
   <dataValidations count="1">
     <dataValidation sqref="L5:L95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
       <formula1>='فهرست‌ها'!$A$7:$A$12</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>RT-001</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>snapshot zeroing task_control</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>برد با MODULE_MEASUREMENT=0 یا ADC نگه‌داشته</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بوت کن (یا ADC را نگه دار تا snapshot نیاید).
+گام ۲: task_control را اجرا کن و snapshot را درست قبل از GetSnapshot بخوان.
+گام ۳: هر 9 فیلد باید صفر باشد: v_in=0، v_bat24=0، v_bat12=0، v_low=0، v_high=0، i1=0، i2=0، input_present=false و valid=false.
+گام ۴: هیچ فیلدی نباید زبالهٔ پشته باشد؛ همین رفتار را در task_comm، task_ui و task_protection هم باید ببینی.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>هر 9 فیلد snapshot صفر: v_in=0 v_bat24=0 v_bat12=0 v_low=0 v_high=0 i1=0 i2=0 input_present=false valid=false</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>امن</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>بدون زباله پشته؛ مانند task_comm/task_ui/task_protection</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>کد بازبینی + host test</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>RT-002</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>snapshot zeroing task_comm</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>برد با measurement خاموش</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>گام ۱: برد را با measurement خاموش بوت کن.
+گام ۲: task_comm را اجرا کن و snapshot را قبل از GetSnapshot بخوان (3 ثانیه).
+گام ۳: هر 9 فیلد باید از قبل صفر شده باشد؛ هیچ فیلد نامشخص (indeterminate) نباید در ساختار باشد.</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>هر 9 فیلد صفر شده قبل از GetSnapshot</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>بدون indeterminate struct</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>کد بازبینی</t>
+        </is>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P6" s="13" t="n"/>
+      <c r="Q6" s="14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>RT-003</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>snapshot zeroing task_ui</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>برد با measurement خاموش</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>گام ۱: برد را با measurement خاموش بوت کن.
+گام ۲: task_ui را اجرا کن (3 ثانیه).
+گام ۳: هر 9 فیلد snapshot باید صفر باشد و خروجی UI باید safe-off باشد؛ یعنی همهٔ LEDها خاموش بمانند.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>هر 9 فیلد صفر؛ UI safe-off</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>safe-off</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>LED خاموش</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>کد بازبینی</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40.5" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>RT-004</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>snapshot zeroing task_protection</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>برد با measurement خاموش</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>گام ۱: برد را با measurement خاموش بوت کن.
+گام ۲: task_protection را اجرا کن (3 ثانیه).
+گام ۳: هر 9 فیلد باید صفر باشد و Protection فقط valid را چک کند؛ هیچ fault کاذبی نباید ساخته شود.</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>3s</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>هر 9 فیلد صفر؛ Protection فقط valid را چک کند</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>بدون fault کاذب</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+      <c r="M8" s="11" t="n"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>کد بازبینی</t>
+        </is>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>RT-005</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>ترتیب اجرا در task_control</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>لینک فعال + شارژر فعال</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>گام ۱: لینک و شارژر را فعال کن تا یک پاس واقعی control اجرا شود.
+گام ۲: یک پاس کامل task_control را با لاگ یا نقطه‌توقف (breakpoint) قدم‌به‌قدم دنبال کن.
+گام ۳: ترتیب اجرا باید دقیقاً این باشد: اول imbalance، بعد fault، بعد خطای فنی شارژر، بعد mcu_power_path، بعد changeover، بعد ارزیابی شارژر و در آخر poll واچ‌داگ.
+گام ۴: پاس باید در همان 10 میلی‌ثانیه تمام شود و ترتیب در همهٔ پاس‌ها حفظ شود.</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>10ms</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>ترتیب ثابت: imbalance -&gt; fault -&gt; charger technical fault -&gt; mcu_power_path -&gt; changeover -&gt; charger evaluate -&gt; watchdog poll</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>ترتیب حفظ شود</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>RT-007</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>بدون HAL_Delay</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>کد</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>گام ۱: در کل پوشهٔ Firmware دنبال HAL_Delay بگرد (grep).
+گام ۲: باید صفر مورد پیدا شود.
+گام ۳: هر تأخیری در کد باید فقط از Rtos_DelayMilliseconds یا osDelayUntil باشد.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>1s</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>هیچ HAL_Delay وجود نداشته باشد؛ فقط Rtos_DelayMilliseconds و osDelayUntil</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>0 مورد HAL_Delay</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>check_ai_rules.sh</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>RT-008</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>تخصیص استاتیک</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>کد</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>گام ۱: فایل‌های rtos_app.c و rtos_config.h را باز کن.
+گام ۲: برای تک‌تک threadها چک کن که با حافظهٔ ثابت ساخته شده‌اند (cb_mem و stack_mem).
+گام ۳: دنبال malloc و free در کد محصول بگرد؛ نباید هیچ‌کدام باشد و heap_4 هم نباید لینک شده باشد.
+گام ۴: نتیجه: فقط تخصیص استاتیک مجاز است.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>1s</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>همه threadها با cb_mem و stack_mem ثابت؛ بدون malloc/free؛ heap_4 لینک نشود</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>static allocation + no malloc</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="n"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>check_ai_rules.sh</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>RT-011</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>تبدیل تیک به ms در چک‌این‌های IWDG</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>کد</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>گام ۱: هر 7 محل check-in و poll واچ‌داگ را در پنج تسک پیدا کن (task_control، task_comm، task_measurement، task_protection و task_ui).
+گام ۲: در هر محل چک کن زمان از تبدیل func__Rtos_TicksToMilliseconds(osKernelGetTickCount()) گذشته باشد، نه تیک خام کرنل.
+گام ۳: با فرکانس تیک فعلی (1000 هرتز) رفتار باید دقیقاً مثل قبل باشد و هر دو گیت (check_ai_rules و check_firmware_syntax) سبز شوند.
+گام ۴ (برد): روی برد واقعی واچ‌داگ را زیر نظر بگیر؛ اگر روزی فرکانس تیک عوض شود، مهلت‌ها خودکار بر حسب میلی‌ثانیه درست می‌مانند. تست برد هنوز در انتظار است.</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>در فرکانس تیک ۱۰۰۰ هرتز رفتار دقیقاً مثل قبل؛ اگر روزی فرکانس تیک عوض شود، مهلت‌های واچ‌داگ خودکار بر حسب ms درست می‌مانند</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>هیچ چک‌اینی تیک خام را جای ms ندهد؛ هر دو گیت سبز</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: هر دو گیت سبز، بودجهٔ RAM/فلش بدون تغییر؛ تست برد: در انتظار</t>
+        </is>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>004fbf1</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="17">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="17">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="17">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="17">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="17">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="17">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="17">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="17">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="17">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="17">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="17">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="17">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="17">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="17">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="17">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="17">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="17">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="17">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="17">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="17">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q12"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -1941,7 +2221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -2037,14 +2317,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId2"/>
+    <hyperlink ref="A2" location="'تست‌های برنامه‌نویسی'!A5"/>
+    <hyperlink ref="B2" location="'تست‌های برنامه‌نویسی'!A5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -2082,7 +2362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -2179,7 +2459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -836,40 +836,39 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>همه تسک‌ها فعال</t>
+          <t>دستگاه کامل وصل است: باتری، برق شهر، بار و پنل</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>گام ۱: همهٔ تسک‌ها را فعال کن و لاگ check-in واچ‌داگ را باز کن.
-گام ۲: 5 ثانیه نگاه کن: فقط task_control کیک (kick) می‌زند؛ بقیهٔ تسک‌ها فقط check-in می‌کنند.
-گام ۳: یکی از تسک‌ها را عمداً stale کن (توقفش بده).
-گام ۴: از آن لحظه نباید دیگر kick زده شود؛ kick فقط وقتی مجاز است که همهٔ تسک‌ها تازه باشند.</t>
+          <t>گام ۱: دستگاه را زیر کار واقعی بگذار (شارژ و بار هم‌زمان).
+گام ۲: چند ساعت رهایش کن؛ هر از چندی سر بزن که چراغ‌ها، پنل و شارژ زنده‌اند.
+گام ۳: آخر کار، یک خطای ۶ بساز و پاک کن تا ببینی همهٔ بخش‌ها هنوز پاسخ می‌دهند.</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>چند ساعت کار واقعی ترکیبی</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>چند ساعت</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>فقط task_control kick می‌زند؛ بقیه تسک‌ها check-in می‌کنند؛ اگر یک تسک stale شود kick انجام نشود</t>
+          <t>در تمام مدت هیچ هنگ و ریستی نیست؛ چراغ‌ها، پنل و شارژ پیوسته و روان کار می‌کنند</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پایداری بلندمدت</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>kick فقط وقتی همه تازه‌اند</t>
+          <t>کار بی‌هنگ چندساعته = قبول؛ هر هنگ یا ریست = رد</t>
         </is>
       </c>
       <c r="K5" s="11" t="n"/>
@@ -910,30 +909,28 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>پنل وصل</t>
+          <t>پنل باز و یک دیالوگ روی صفحه است</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>گام ۱: پنل را وصل کن.
-گام ۲: یک دیالوگ تأیید بساز (مثلاً دکمهٔ قطع PWM را بزن).
-گام ۳: دیالوگ باید تیره (#pmod) باشد و متنش بگوید Enter تأیید و Esc انصراف است.
-گام ۴: یک بار Enter بزن (تأیید کند) و یک بار در دفعهٔ بعد Esc (لغو کند)؛ هر دو باید کار کنند.</t>
+          <t>گام ۱: دیالوگ را با Enter تأیید کن و نتیجه را ببین.
+گام ۲: دوباره بازش کن و این بار با Esc ببند.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>کلیک قطع</t>
+          <t>Enter و Esc روی دیالوگ پنل</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>3s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>دیالوگ تیره #pmod با متن Enter=تأیید Esc=انصراف؛ Enter تأیید و Esc لغو کند</t>
+          <t>Enter یعنی تأیید و Esc یعنی لغو؛ هر دو تمیز و بدون اثر اضافه کار می‌کنند</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +940,7 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Enter/Esc کار کند + استایل تیره</t>
+          <t>رفتار درست هر دو کلید = قبول؛ برعکس یا بی‌اثر = رد</t>
         </is>
       </c>
       <c r="K6" s="6" t="n"/>
@@ -984,40 +981,38 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>پنل وصل</t>
+          <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>گام ۱: پنل را وصل کن.
-گام ۲: دو دیالوگ تأیید پشت سر هم بساز (دو درخواست نزدیک به هم).
-گام ۳: 5 ثانیه نگاه کن: دیالوگ‌ها باید یکی‌یکی و به نوبت (Promise queue) بیایند.
-گام ۴: هیچ‌وقت دو دیالوگ نباید روی هم بیفتند.</t>
+          <t>گام ۱: پشت سر هم چند پیام و دیالوگ بساز.
+گام ۲: به ترتیب نمایش و بسته‌شدنشان دقت کن.</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>دو درخواست</t>
+          <t>چند دیالوگ پشت سر هم</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>5s</t>
+          <t>پنج دقیقه</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>دیالوگ‌ها با Promise queue یکی‌یکی بیایند، نه روی هم</t>
+          <t>پیام‌ها نوبتی و کامل نشان داده می‌شوند؛ هیچ‌کدام گم یا روی هم خراب نمی‌شوند</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>صف</t>
+          <t>صف مرتب</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>بدون همپوشانی</t>
+          <t>نمایش نوبتی کامل = قبول؛ گم‌شدن پیام = رد</t>
         </is>
       </c>
       <c r="K7" s="11" t="n"/>

--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,6 +93,57 @@
     <font>
       <name val="Tahoma"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="8">
@@ -159,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -212,6 +263,56 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -583,90 +684,114 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Rtos — تسک‌ها، snapshot zeroing، watchdog، ترتیب اجرا</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="n"/>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>هدف: اثبات اینکه تسک‌های CMSIS-RTOS2 ساده، خوانا، بدون HAL_Delay، با تخصیص استاتیک و zero کردن کامل snapshot کار می‌کنند</t>
         </is>
       </c>
-    </row>
-    <row r="4"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="n"/>
+      <c r="B4" s="22" t="n"/>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="22" t="n"/>
+    </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>قوانین: هر تست باید پیش‌شرط، ورودی، انتظار، معیار قبولی صریح داشته باشد؛ نتیجه واقعی فقط با اندازه‌گیری روی برد</t>
         </is>
       </c>
-    </row>
-    <row r="6"/>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n"/>
+      <c r="B6" s="22" t="n"/>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+    </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>نسخه</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>شرح تغییر</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>ایجاد اولیه Rtos_Validation — snapshot zeroing task_control (CO-023)، watchdog poll، ترتیب imbalance-&gt;fault-&gt;changeover-&gt;charger، static allocation</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>9cb64eb</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>اضافه شدن RT-008..RT-010 برای panel dialog و Enter/Esc</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
@@ -711,566 +836,1254 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Rtos</t>
         </is>
       </c>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="22" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="G1" s="22" t="n"/>
+      <c r="H1" s="22" t="n"/>
+      <c r="I1" s="22" t="n"/>
+      <c r="J1" s="22" t="n"/>
+      <c r="K1" s="22" t="n"/>
+      <c r="L1" s="22" t="n"/>
+      <c r="M1" s="22" t="n"/>
+      <c r="N1" s="22" t="n"/>
+      <c r="O1" s="22" t="n"/>
+      <c r="P1" s="22" t="n"/>
+      <c r="Q1" s="22" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="22" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="22" t="n"/>
+      <c r="K2" s="22" t="n"/>
+      <c r="L2" s="22" t="n"/>
+      <c r="M2" s="22" t="n"/>
+      <c r="N2" s="22" t="n"/>
+      <c r="O2" s="22" t="n"/>
+      <c r="P2" s="22" t="n"/>
+      <c r="Q2" s="22" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="22" t="n"/>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="22" t="n"/>
+      <c r="K3" s="22" t="n"/>
+      <c r="L3" s="22" t="n"/>
+      <c r="M3" s="22" t="n"/>
+      <c r="N3" s="22" t="n"/>
+      <c r="O3" s="22" t="n"/>
+      <c r="P3" s="22" t="n"/>
+      <c r="Q3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="25" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="25" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="25" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>RT-006</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>watchdog poll و check-in</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>دستگاه کامل وصل است: باتری، برق شهر، بار و پنل</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را زیر کار واقعی بگذار (شارژ و بار هم‌زمان).
 گام ۲: چند ساعت رهایش کن؛ هر از چندی سر بزن که چراغ‌ها، پنل و شارژ زنده‌اند.
 گام ۳: آخر کار، یک خطای ۶ بساز و پاک کن تا ببینی همهٔ بخش‌ها هنوز پاسخ می‌دهند.</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>چند ساعت کار واقعی ترکیبی</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>چند ساعت</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>در تمام مدت هیچ هنگ و ریستی نیست؛ چراغ‌ها، پنل و شارژ پیوسته و روان کار می‌کنند</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>پایداری بلندمدت</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>کار بی‌هنگ چندساعته = قبول؛ هر هنگ یا ریست = رد</t>
         </is>
       </c>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="15" t="inlineStr">
+      <c r="K5" s="27" t="n"/>
+      <c r="L5" s="30" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="13" t="inlineStr">
+      <c r="M5" s="27" t="n"/>
+      <c r="N5" s="27" t="n"/>
+      <c r="O5" s="29" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="14" t="inlineStr">
+      <c r="P5" s="29" t="n"/>
+      <c r="Q5" s="31" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>RT-009</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>panel dialog Enter/Esc</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>پنل باز و یک دیالوگ روی صفحه است</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>گام ۱: دیالوگ را با Enter تأیید کن و نتیجه را ببین.
 گام ۲: دوباره بازش کن و این بار با Esc ببند.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>Enter و Esc روی دیالوگ پنل</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="32" t="inlineStr">
         <is>
           <t>Enter یعنی تأیید و Esc یعنی لغو؛ هر دو تمیز و بدون اثر اضافه کار می‌کنند</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" s="32" t="inlineStr">
         <is>
           <t>رفتار درست هر دو کلید = قبول؛ برعکس یا بی‌اثر = رد</t>
         </is>
       </c>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="16" t="inlineStr">
+      <c r="K6" s="32" t="n"/>
+      <c r="L6" s="34" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="M6" s="32" t="n"/>
+      <c r="N6" s="32" t="n"/>
+      <c r="O6" s="33" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P6" s="8" t="n"/>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="35" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>RT-010</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>panel dialog queue PMQ</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>پنل باز و دستگاه روشن است</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>گام ۱: پشت سر هم چند پیام و دیالوگ بساز.
 گام ۲: به ترتیب نمایش و بسته‌شدنشان دقت کن.</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>چند دیالوگ پشت سر هم</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>پنج دقیقه</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>پیام‌ها نوبتی و کامل نشان داده می‌شوند؛ هیچ‌کدام گم یا روی هم خراب نمی‌شوند</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>صف مرتب</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>نمایش نوبتی کامل = قبول؛ گم‌شدن پیام = رد</t>
         </is>
       </c>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="K7" s="27" t="n"/>
+      <c r="L7" s="34" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="13" t="inlineStr">
+      <c r="M7" s="27" t="n"/>
+      <c r="N7" s="27" t="n"/>
+      <c r="O7" s="29" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P7" s="13" t="n"/>
-      <c r="Q7" s="14" t="inlineStr">
+      <c r="P7" s="29" t="n"/>
+      <c r="Q7" s="31" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.5" customHeight="1">
-      <c r="Q8" s="17">
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="22" t="n"/>
+      <c r="L8" s="22" t="n"/>
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="22" t="n"/>
+      <c r="Q8" s="36">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="Q9" s="17">
+      <c r="A9" s="22" t="n"/>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="22" t="n"/>
+      <c r="K9" s="22" t="n"/>
+      <c r="L9" s="22" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="22" t="n"/>
+      <c r="P9" s="22" t="n"/>
+      <c r="Q9" s="36">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="Q10" s="17">
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="36">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="40.5" customHeight="1">
-      <c r="Q11" s="17">
+      <c r="A11" s="22" t="n"/>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="36">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="Q12" s="17">
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="22" t="n"/>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="36">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="Q13" s="17">
+      <c r="A13" s="22" t="n"/>
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="22" t="n"/>
+      <c r="K13" s="22" t="n"/>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="22" t="n"/>
+      <c r="N13" s="22" t="n"/>
+      <c r="O13" s="22" t="n"/>
+      <c r="P13" s="22" t="n"/>
+      <c r="Q13" s="36">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="Q14" s="17">
+      <c r="A14" s="22" t="n"/>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="36">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="Q15" s="17">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="22" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="22" t="n"/>
+      <c r="Q15" s="36">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="17">
+      <c r="A16" s="22" t="n"/>
+      <c r="B16" s="22" t="n"/>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="22" t="n"/>
+      <c r="K16" s="22" t="n"/>
+      <c r="L16" s="22" t="n"/>
+      <c r="M16" s="22" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="22" t="n"/>
+      <c r="P16" s="22" t="n"/>
+      <c r="Q16" s="36">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="17">
+      <c r="A17" s="22" t="n"/>
+      <c r="B17" s="22" t="n"/>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="22" t="n"/>
+      <c r="L17" s="22" t="n"/>
+      <c r="M17" s="22" t="n"/>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="22" t="n"/>
+      <c r="Q17" s="36">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="17">
+      <c r="A18" s="22" t="n"/>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22" t="n"/>
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="36">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="17">
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="36">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="17">
+      <c r="A20" s="22" t="n"/>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="36">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="17">
+      <c r="A21" s="22" t="n"/>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="36">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="17">
+      <c r="A22" s="22" t="n"/>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="22" t="n"/>
+      <c r="K22" s="22" t="n"/>
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="22" t="n"/>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="22" t="n"/>
+      <c r="P22" s="22" t="n"/>
+      <c r="Q22" s="36">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="17">
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="22" t="n"/>
+      <c r="L23" s="22" t="n"/>
+      <c r="M23" s="22" t="n"/>
+      <c r="N23" s="22" t="n"/>
+      <c r="O23" s="22" t="n"/>
+      <c r="P23" s="22" t="n"/>
+      <c r="Q23" s="36">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="17">
+      <c r="A24" s="22" t="n"/>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22" t="n"/>
+      <c r="P24" s="22" t="n"/>
+      <c r="Q24" s="36">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="17">
+      <c r="A25" s="22" t="n"/>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="22" t="n"/>
+      <c r="K25" s="22" t="n"/>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="22" t="n"/>
+      <c r="N25" s="22" t="n"/>
+      <c r="O25" s="22" t="n"/>
+      <c r="P25" s="22" t="n"/>
+      <c r="Q25" s="36">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="17">
+      <c r="A26" s="22" t="n"/>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="22" t="n"/>
+      <c r="K26" s="22" t="n"/>
+      <c r="L26" s="22" t="n"/>
+      <c r="M26" s="22" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="22" t="n"/>
+      <c r="P26" s="22" t="n"/>
+      <c r="Q26" s="36">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="17">
+      <c r="A27" s="22" t="n"/>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="22" t="n"/>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="22" t="n"/>
+      <c r="N27" s="22" t="n"/>
+      <c r="O27" s="22" t="n"/>
+      <c r="P27" s="22" t="n"/>
+      <c r="Q27" s="36">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="17">
+      <c r="A28" s="22" t="n"/>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="22" t="n"/>
+      <c r="N28" s="22" t="n"/>
+      <c r="O28" s="22" t="n"/>
+      <c r="P28" s="22" t="n"/>
+      <c r="Q28" s="36">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="17">
+      <c r="A29" s="22" t="n"/>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="22" t="n"/>
+      <c r="K29" s="22" t="n"/>
+      <c r="L29" s="22" t="n"/>
+      <c r="M29" s="22" t="n"/>
+      <c r="N29" s="22" t="n"/>
+      <c r="O29" s="22" t="n"/>
+      <c r="P29" s="22" t="n"/>
+      <c r="Q29" s="36">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="17">
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="22" t="n"/>
+      <c r="K30" s="22" t="n"/>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="22" t="n"/>
+      <c r="N30" s="22" t="n"/>
+      <c r="O30" s="22" t="n"/>
+      <c r="P30" s="22" t="n"/>
+      <c r="Q30" s="36">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="17">
+      <c r="A31" s="22" t="n"/>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="22" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="22" t="n"/>
+      <c r="N31" s="22" t="n"/>
+      <c r="O31" s="22" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="36">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="17">
+      <c r="A32" s="22" t="n"/>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="22" t="n"/>
+      <c r="K32" s="22" t="n"/>
+      <c r="L32" s="22" t="n"/>
+      <c r="M32" s="22" t="n"/>
+      <c r="N32" s="22" t="n"/>
+      <c r="O32" s="22" t="n"/>
+      <c r="P32" s="22" t="n"/>
+      <c r="Q32" s="36">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="17">
+      <c r="A33" s="22" t="n"/>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="22" t="n"/>
+      <c r="K33" s="22" t="n"/>
+      <c r="L33" s="22" t="n"/>
+      <c r="M33" s="22" t="n"/>
+      <c r="N33" s="22" t="n"/>
+      <c r="O33" s="22" t="n"/>
+      <c r="P33" s="22" t="n"/>
+      <c r="Q33" s="36">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="17">
+      <c r="A34" s="22" t="n"/>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="22" t="n"/>
+      <c r="K34" s="22" t="n"/>
+      <c r="L34" s="22" t="n"/>
+      <c r="M34" s="22" t="n"/>
+      <c r="N34" s="22" t="n"/>
+      <c r="O34" s="22" t="n"/>
+      <c r="P34" s="22" t="n"/>
+      <c r="Q34" s="36">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="17">
+      <c r="A35" s="22" t="n"/>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="22" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="22" t="n"/>
+      <c r="K35" s="22" t="n"/>
+      <c r="L35" s="22" t="n"/>
+      <c r="M35" s="22" t="n"/>
+      <c r="N35" s="22" t="n"/>
+      <c r="O35" s="22" t="n"/>
+      <c r="P35" s="22" t="n"/>
+      <c r="Q35" s="36">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="17">
+      <c r="A36" s="22" t="n"/>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="22" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="22" t="n"/>
+      <c r="K36" s="22" t="n"/>
+      <c r="L36" s="22" t="n"/>
+      <c r="M36" s="22" t="n"/>
+      <c r="N36" s="22" t="n"/>
+      <c r="O36" s="22" t="n"/>
+      <c r="P36" s="22" t="n"/>
+      <c r="Q36" s="36">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="17">
+      <c r="A37" s="22" t="n"/>
+      <c r="B37" s="22" t="n"/>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="22" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="22" t="n"/>
+      <c r="K37" s="22" t="n"/>
+      <c r="L37" s="22" t="n"/>
+      <c r="M37" s="22" t="n"/>
+      <c r="N37" s="22" t="n"/>
+      <c r="O37" s="22" t="n"/>
+      <c r="P37" s="22" t="n"/>
+      <c r="Q37" s="36">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="17">
+      <c r="A38" s="22" t="n"/>
+      <c r="B38" s="22" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="22" t="n"/>
+      <c r="K38" s="22" t="n"/>
+      <c r="L38" s="22" t="n"/>
+      <c r="M38" s="22" t="n"/>
+      <c r="N38" s="22" t="n"/>
+      <c r="O38" s="22" t="n"/>
+      <c r="P38" s="22" t="n"/>
+      <c r="Q38" s="36">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="17">
+      <c r="A39" s="22" t="n"/>
+      <c r="B39" s="22" t="n"/>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="22" t="n"/>
+      <c r="H39" s="22" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="22" t="n"/>
+      <c r="K39" s="22" t="n"/>
+      <c r="L39" s="22" t="n"/>
+      <c r="M39" s="22" t="n"/>
+      <c r="N39" s="22" t="n"/>
+      <c r="O39" s="22" t="n"/>
+      <c r="P39" s="22" t="n"/>
+      <c r="Q39" s="36">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="17">
+      <c r="A40" s="22" t="n"/>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
+      <c r="G40" s="22" t="n"/>
+      <c r="H40" s="22" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="22" t="n"/>
+      <c r="K40" s="22" t="n"/>
+      <c r="L40" s="22" t="n"/>
+      <c r="M40" s="22" t="n"/>
+      <c r="N40" s="22" t="n"/>
+      <c r="O40" s="22" t="n"/>
+      <c r="P40" s="22" t="n"/>
+      <c r="Q40" s="36">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="17">
+      <c r="A41" s="22" t="n"/>
+      <c r="B41" s="22" t="n"/>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="22" t="n"/>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="22" t="n"/>
+      <c r="H41" s="22" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="22" t="n"/>
+      <c r="K41" s="22" t="n"/>
+      <c r="L41" s="22" t="n"/>
+      <c r="M41" s="22" t="n"/>
+      <c r="N41" s="22" t="n"/>
+      <c r="O41" s="22" t="n"/>
+      <c r="P41" s="22" t="n"/>
+      <c r="Q41" s="36">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="17">
+      <c r="A42" s="22" t="n"/>
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
+      <c r="G42" s="22" t="n"/>
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="22" t="n"/>
+      <c r="K42" s="22" t="n"/>
+      <c r="L42" s="22" t="n"/>
+      <c r="M42" s="22" t="n"/>
+      <c r="N42" s="22" t="n"/>
+      <c r="O42" s="22" t="n"/>
+      <c r="P42" s="22" t="n"/>
+      <c r="Q42" s="36">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="17">
+      <c r="A43" s="22" t="n"/>
+      <c r="B43" s="22" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="22" t="n"/>
+      <c r="G43" s="22" t="n"/>
+      <c r="H43" s="22" t="n"/>
+      <c r="I43" s="22" t="n"/>
+      <c r="J43" s="22" t="n"/>
+      <c r="K43" s="22" t="n"/>
+      <c r="L43" s="22" t="n"/>
+      <c r="M43" s="22" t="n"/>
+      <c r="N43" s="22" t="n"/>
+      <c r="O43" s="22" t="n"/>
+      <c r="P43" s="22" t="n"/>
+      <c r="Q43" s="36">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="17">
+      <c r="A44" s="22" t="n"/>
+      <c r="B44" s="22" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="22" t="n"/>
+      <c r="K44" s="22" t="n"/>
+      <c r="L44" s="22" t="n"/>
+      <c r="M44" s="22" t="n"/>
+      <c r="N44" s="22" t="n"/>
+      <c r="O44" s="22" t="n"/>
+      <c r="P44" s="22" t="n"/>
+      <c r="Q44" s="36">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="17">
+      <c r="A45" s="22" t="n"/>
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="22" t="n"/>
+      <c r="H45" s="22" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="22" t="n"/>
+      <c r="K45" s="22" t="n"/>
+      <c r="L45" s="22" t="n"/>
+      <c r="M45" s="22" t="n"/>
+      <c r="N45" s="22" t="n"/>
+      <c r="O45" s="22" t="n"/>
+      <c r="P45" s="22" t="n"/>
+      <c r="Q45" s="36">
         <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="Q46" s="17">
+      <c r="A46" s="22" t="n"/>
+      <c r="B46" s="22" t="n"/>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="22" t="n"/>
+      <c r="F46" s="22" t="n"/>
+      <c r="G46" s="22" t="n"/>
+      <c r="H46" s="22" t="n"/>
+      <c r="I46" s="22" t="n"/>
+      <c r="J46" s="22" t="n"/>
+      <c r="K46" s="22" t="n"/>
+      <c r="L46" s="22" t="n"/>
+      <c r="M46" s="22" t="n"/>
+      <c r="N46" s="22" t="n"/>
+      <c r="O46" s="22" t="n"/>
+      <c r="P46" s="22" t="n"/>
+      <c r="Q46" s="36">
         <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="Q47" s="17">
+      <c r="A47" s="22" t="n"/>
+      <c r="B47" s="22" t="n"/>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="22" t="n"/>
+      <c r="F47" s="22" t="n"/>
+      <c r="G47" s="22" t="n"/>
+      <c r="H47" s="22" t="n"/>
+      <c r="I47" s="22" t="n"/>
+      <c r="J47" s="22" t="n"/>
+      <c r="K47" s="22" t="n"/>
+      <c r="L47" s="22" t="n"/>
+      <c r="M47" s="22" t="n"/>
+      <c r="N47" s="22" t="n"/>
+      <c r="O47" s="22" t="n"/>
+      <c r="P47" s="22" t="n"/>
+      <c r="Q47" s="36">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
@@ -1317,129 +2130,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
+      <c r="B1" s="22" t="n"/>
+      <c r="C1" s="22" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="22" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="G1" s="22" t="n"/>
+      <c r="H1" s="22" t="n"/>
+      <c r="I1" s="22" t="n"/>
+      <c r="J1" s="22" t="n"/>
+      <c r="K1" s="22" t="n"/>
+      <c r="L1" s="22" t="n"/>
+      <c r="M1" s="22" t="n"/>
+      <c r="N1" s="22" t="n"/>
+      <c r="O1" s="22" t="n"/>
+      <c r="P1" s="22" t="n"/>
+      <c r="Q1" s="22" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="19" t="inlineStr">
+      <c r="A2" s="22" t="n"/>
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="22" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="22" t="n"/>
+      <c r="K2" s="22" t="n"/>
+      <c r="L2" s="22" t="n"/>
+      <c r="M2" s="22" t="n"/>
+      <c r="N2" s="22" t="n"/>
+      <c r="O2" s="22" t="n"/>
+      <c r="P2" s="22" t="n"/>
+      <c r="Q2" s="22" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="22" t="n"/>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="22" t="n"/>
+      <c r="K3" s="22" t="n"/>
+      <c r="L3" s="22" t="n"/>
+      <c r="M3" s="22" t="n"/>
+      <c r="N3" s="22" t="n"/>
+      <c r="O3" s="22" t="n"/>
+      <c r="P3" s="22" t="n"/>
+      <c r="Q3" s="22" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="25" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="25" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="25" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>RT-001</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>snapshot zeroing task_control</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>برد با MODULE_MEASUREMENT=0 یا ADC نگه‌داشته</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بوت کن (یا ADC را نگه دار تا snapshot نیاید).
 گام ۲: task_control را اجرا کن و snapshot را درست قبل از GetSnapshot بخوان.
@@ -1447,308 +2310,308 @@
 گام ۴: هیچ فیلدی نباید زبالهٔ پشته باشد؛ همین رفتار را در task_comm، task_ui و task_protection هم باید ببینی.</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>هر 9 فیلد snapshot صفر: v_in=0 v_bat24=0 v_bat12=0 v_low=0 v_high=0 i1=0 i2=0 input_present=false valid=false</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>امن</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="32" t="inlineStr">
         <is>
           <t>بدون زباله پشته؛ مانند task_comm/task_ui/task_protection</t>
         </is>
       </c>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="K5" s="32" t="n"/>
+      <c r="L5" s="39" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="M5" s="6" t="n"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="M5" s="32" t="n"/>
+      <c r="N5" s="32" t="inlineStr">
         <is>
           <t>کد بازبینی + host test</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P5" s="8" t="n"/>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="35" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>RT-002</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>snapshot zeroing task_comm</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>برد با measurement خاموش</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>گام ۱: برد را با measurement خاموش بوت کن.
 گام ۲: task_comm را اجرا کن و snapshot را قبل از GetSnapshot بخوان (3 ثانیه).
 گام ۳: هر 9 فیلد باید از قبل صفر شده باشد؛ هیچ فیلد نامشخص (indeterminate) نباید در ساختار باشد.</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>هر 9 فیلد صفر شده قبل از GetSnapshot</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="27" t="inlineStr">
         <is>
           <t>بدون indeterminate struct</t>
         </is>
       </c>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="K6" s="27" t="n"/>
+      <c r="L6" s="39" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="M6" s="11" t="n"/>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="M6" s="27" t="n"/>
+      <c r="N6" s="27" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O6" s="13" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="14" t="inlineStr">
+      <c r="P6" s="29" t="n"/>
+      <c r="Q6" s="31" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>RT-003</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>snapshot zeroing task_ui</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>برد با measurement خاموش</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>گام ۱: برد را با measurement خاموش بوت کن.
 گام ۲: task_ui را اجرا کن (3 ثانیه).
 گام ۳: هر 9 فیلد snapshot باید صفر باشد و خروجی UI باید safe-off باشد؛ یعنی همهٔ LEDها خاموش بمانند.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="33" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="32" t="inlineStr">
         <is>
           <t>هر 9 فیلد صفر؛ UI safe-off</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="32" t="inlineStr">
         <is>
           <t>safe-off</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="32" t="inlineStr">
         <is>
           <t>LED خاموش</t>
         </is>
       </c>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="K7" s="32" t="n"/>
+      <c r="L7" s="39" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="M7" s="32" t="n"/>
+      <c r="N7" s="32" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="33" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P7" s="8" t="n"/>
-      <c r="Q7" s="10" t="inlineStr">
+      <c r="P7" s="33" t="n"/>
+      <c r="Q7" s="35" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.5" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>RT-004</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>snapshot zeroing task_protection</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>برد با measurement خاموش</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>گام ۱: برد را با measurement خاموش بوت کن.
 گام ۲: task_protection را اجرا کن (3 ثانیه).
 گام ۳: هر 9 فیلد باید صفر باشد و Protection فقط valid را چک کند؛ هیچ fault کاذبی نباید ساخته شود.</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>هر 9 فیلد صفر؛ Protection فقط valid را چک کند</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="27" t="inlineStr">
         <is>
           <t>بدون fault کاذب</t>
         </is>
       </c>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="K8" s="27" t="n"/>
+      <c r="L8" s="39" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="M8" s="27" t="n"/>
+      <c r="N8" s="27" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O8" s="29" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="14" t="inlineStr">
+      <c r="P8" s="29" t="n"/>
+      <c r="Q8" s="31" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>RT-005</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>ترتیب اجرا در task_control</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>لینک فعال + شارژر فعال</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>گام ۱: لینک و شارژر را فعال کن تا یک پاس واقعی control اجرا شود.
 گام ۲: یک پاس کامل task_control را با لاگ یا نقطه‌توقف (breakpoint) قدم‌به‌قدم دنبال کن.
@@ -1756,150 +2619,150 @@
 گام ۴: پاس باید در همان 10 میلی‌ثانیه تمام شود و ترتیب در همهٔ پاس‌ها حفظ شود.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>ترتیب ثابت: imbalance -&gt; fault -&gt; charger technical fault -&gt; mcu_power_path -&gt; changeover -&gt; charger evaluate -&gt; watchdog poll</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" s="32" t="inlineStr">
         <is>
           <t>ترتیب حفظ شود</t>
         </is>
       </c>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="15" t="inlineStr">
+      <c r="K9" s="32" t="n"/>
+      <c r="L9" s="30" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="M9" s="32" t="n"/>
+      <c r="N9" s="32" t="n"/>
+      <c r="O9" s="33" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P9" s="8" t="n"/>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="P9" s="33" t="n"/>
+      <c r="Q9" s="35" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>RT-007</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>بدون HAL_Delay</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>کد</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>گام ۱: در کل پوشهٔ Firmware دنبال HAL_Delay بگرد (grep).
 گام ۲: باید صفر مورد پیدا شود.
 گام ۳: هر تأخیری در کد باید فقط از Rtos_DelayMilliseconds یا osDelayUntil باشد.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="33" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="32" t="inlineStr">
         <is>
           <t>هیچ HAL_Delay وجود نداشته باشد؛ فقط Rtos_DelayMilliseconds و osDelayUntil</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" s="32" t="inlineStr">
         <is>
           <t>0 مورد HAL_Delay</t>
         </is>
       </c>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="K10" s="32" t="n"/>
+      <c r="L10" s="39" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="inlineStr">
+      <c r="M10" s="32" t="n"/>
+      <c r="N10" s="32" t="inlineStr">
         <is>
           <t>check_ai_rules.sh</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="33" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P10" s="8" t="n"/>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="P10" s="33" t="n"/>
+      <c r="Q10" s="35" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>RT-008</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>تخصیص استاتیک</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>کد</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="40" t="inlineStr">
         <is>
           <t>گام ۱: فایل‌های rtos_app.c و rtos_config.h را باز کن.
 گام ۲: برای تک‌تک threadها چک کن که با حافظهٔ ثابت ساخته شده‌اند (cb_mem و stack_mem).
@@ -1907,77 +2770,77 @@
 گام ۴: نتیجه: فقط تخصیص استاتیک مجاز است.</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>همه threadها با cb_mem و stack_mem ثابت؛ بدون malloc/free؛ heap_4 لینک نشود</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="27" t="inlineStr">
         <is>
           <t>static allocation + no malloc</t>
         </is>
       </c>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="K11" s="27" t="n"/>
+      <c r="L11" s="39" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="M11" s="27" t="n"/>
+      <c r="N11" s="27" t="inlineStr">
         <is>
           <t>check_ai_rules.sh</t>
         </is>
       </c>
-      <c r="O11" s="13" t="inlineStr">
+      <c r="O11" s="29" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P11" s="13" t="n"/>
-      <c r="Q11" s="14" t="inlineStr">
+      <c r="P11" s="29" t="n"/>
+      <c r="Q11" s="31" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>RT-011</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>تبدیل تیک به ms در چک‌این‌های IWDG</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>کد</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>گام ۱: هر 7 محل check-in و poll واچ‌داگ را در پنج تسک پیدا کن (task_control، task_comm، task_measurement، task_protection و task_ui).
 گام ۲: در هر محل چک کن زمان از تبدیل func__Rtos_TicksToMilliseconds(osKernelGetTickCount()) گذشته باشد، نه تیک خام کرنل.
@@ -1985,171 +2848,491 @@
 گام ۴ (برد): روی برد واقعی واچ‌داگ را زیر نظر بگیر؛ اگر روزی فرکانس تیک عوض شود، مهلت‌ها خودکار بر حسب میلی‌ثانیه درست می‌مانند. تست برد هنوز در انتظار است.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="32" t="inlineStr">
         <is>
           <t>در فرکانس تیک ۱۰۰۰ هرتز رفتار دقیقاً مثل قبل؛ اگر روزی فرکانس تیک عوض شود، مهلت‌های واچ‌داگ خودکار بر حسب ms درست می‌مانند</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J12" s="32" t="inlineStr">
         <is>
           <t>هیچ چک‌اینی تیک خام را جای ms ندهد؛ هر دو گیت سبز</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="K12" s="32" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: هر دو گیت سبز، بودجهٔ RAM/فلش بدون تغییر؛ تست برد: در انتظار</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="M12" s="32" t="n"/>
+      <c r="N12" s="32" t="n"/>
+      <c r="O12" s="33" t="inlineStr">
         <is>
           <t>004fbf1</t>
         </is>
       </c>
-      <c r="P12" s="8" t="n"/>
-      <c r="Q12" s="10" t="inlineStr">
+      <c r="P12" s="33" t="n"/>
+      <c r="Q12" s="35" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="17">
+      <c r="A13" s="22" t="n"/>
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="22" t="n"/>
+      <c r="K13" s="22" t="n"/>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="22" t="n"/>
+      <c r="N13" s="22" t="n"/>
+      <c r="O13" s="22" t="n"/>
+      <c r="P13" s="22" t="n"/>
+      <c r="Q13" s="36">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="17">
+      <c r="A14" s="22" t="n"/>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="36">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="17">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="22" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="22" t="n"/>
+      <c r="Q15" s="36">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="17">
+      <c r="A16" s="22" t="n"/>
+      <c r="B16" s="22" t="n"/>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="22" t="n"/>
+      <c r="K16" s="22" t="n"/>
+      <c r="L16" s="22" t="n"/>
+      <c r="M16" s="22" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="22" t="n"/>
+      <c r="P16" s="22" t="n"/>
+      <c r="Q16" s="36">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="17">
+      <c r="A17" s="22" t="n"/>
+      <c r="B17" s="22" t="n"/>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="22" t="n"/>
+      <c r="L17" s="22" t="n"/>
+      <c r="M17" s="22" t="n"/>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="22" t="n"/>
+      <c r="Q17" s="36">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="17">
+      <c r="A18" s="22" t="n"/>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22" t="n"/>
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="36">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="17">
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="36">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="17">
+      <c r="A20" s="22" t="n"/>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="36">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="17">
+      <c r="A21" s="22" t="n"/>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="36">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="17">
+      <c r="A22" s="22" t="n"/>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="22" t="n"/>
+      <c r="K22" s="22" t="n"/>
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="22" t="n"/>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="22" t="n"/>
+      <c r="P22" s="22" t="n"/>
+      <c r="Q22" s="36">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="17">
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="22" t="n"/>
+      <c r="L23" s="22" t="n"/>
+      <c r="M23" s="22" t="n"/>
+      <c r="N23" s="22" t="n"/>
+      <c r="O23" s="22" t="n"/>
+      <c r="P23" s="22" t="n"/>
+      <c r="Q23" s="36">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="17">
+      <c r="A24" s="22" t="n"/>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22" t="n"/>
+      <c r="P24" s="22" t="n"/>
+      <c r="Q24" s="36">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="17">
+      <c r="A25" s="22" t="n"/>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="22" t="n"/>
+      <c r="K25" s="22" t="n"/>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="22" t="n"/>
+      <c r="N25" s="22" t="n"/>
+      <c r="O25" s="22" t="n"/>
+      <c r="P25" s="22" t="n"/>
+      <c r="Q25" s="36">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="17">
+      <c r="A26" s="22" t="n"/>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="22" t="n"/>
+      <c r="K26" s="22" t="n"/>
+      <c r="L26" s="22" t="n"/>
+      <c r="M26" s="22" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="22" t="n"/>
+      <c r="P26" s="22" t="n"/>
+      <c r="Q26" s="36">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="17">
+      <c r="A27" s="22" t="n"/>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="22" t="n"/>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="22" t="n"/>
+      <c r="N27" s="22" t="n"/>
+      <c r="O27" s="22" t="n"/>
+      <c r="P27" s="22" t="n"/>
+      <c r="Q27" s="36">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="17">
+      <c r="A28" s="22" t="n"/>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="22" t="n"/>
+      <c r="N28" s="22" t="n"/>
+      <c r="O28" s="22" t="n"/>
+      <c r="P28" s="22" t="n"/>
+      <c r="Q28" s="36">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="17">
+      <c r="A29" s="22" t="n"/>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="22" t="n"/>
+      <c r="K29" s="22" t="n"/>
+      <c r="L29" s="22" t="n"/>
+      <c r="M29" s="22" t="n"/>
+      <c r="N29" s="22" t="n"/>
+      <c r="O29" s="22" t="n"/>
+      <c r="P29" s="22" t="n"/>
+      <c r="Q29" s="36">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="17">
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="22" t="n"/>
+      <c r="K30" s="22" t="n"/>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="22" t="n"/>
+      <c r="N30" s="22" t="n"/>
+      <c r="O30" s="22" t="n"/>
+      <c r="P30" s="22" t="n"/>
+      <c r="Q30" s="36">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="17">
+      <c r="A31" s="22" t="n"/>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="22" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="22" t="n"/>
+      <c r="N31" s="22" t="n"/>
+      <c r="O31" s="22" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="36">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="17">
+      <c r="A32" s="22" t="n"/>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="22" t="n"/>
+      <c r="K32" s="22" t="n"/>
+      <c r="L32" s="22" t="n"/>
+      <c r="M32" s="22" t="n"/>
+      <c r="N32" s="22" t="n"/>
+      <c r="O32" s="22" t="n"/>
+      <c r="P32" s="22" t="n"/>
+      <c r="Q32" s="36">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
@@ -2177,35 +3360,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>مرجع سناریوهای Rtos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>task_control: snapshot zeroing مانند task_comm/task_ui/task_protection — هر 9 فیلد صفر قبل از GetSnapshot</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>task_control ترتیب: imbalance (prev state) -&gt; fault evaluate -&gt; jitter run -&gt; charger technical fault -&gt; mcu_power_path -&gt; imbalance evaluate -&gt; changeover evaluate -&gt; charger evaluate -&gt; watchdog poll</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>watchdog: BSP_IWDG_SLOT_* check-in در هر تسک؛ PollKick فقط در control</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>RTOS: CMSIS-RTOS2 با osDelayUntil و MillisecondsToTicks، بدون فرض tick=1ms</t>
         </is>
@@ -2227,84 +3410,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>شناسه ایراد</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>تاریخ ثبت</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>تاریخ رفع</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>commit رفع</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>BUG-RT-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>RT-001</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>task_control فقط valid=false می‌کرد، 8 فیلد دیگر زباله پشته داشت — latent defect</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>رفع شد</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="21" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
@@ -2330,23 +3513,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Rtos</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="22" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>این برگه پس از پر شدن ستون نتیجه واقعی در برنامه تست و رفع ایرادهای ثبت شده امضا می‌شود</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" s="22" t="n"/>
+    </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
@@ -2368,78 +3555,80 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>فهرست ثابت‌ها و آستانه‌های Rtos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>TASK_STACK_* در rtos_config.h با واحد word — UI/MEASUREMENT/PROTECTION/CONTROL/COMM</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>APP_CONFIG.control_period_ms=10u protection=5u comm=100u</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>BSP_IWDG_STALE_MS و SLOT_* در bsp_iwdg.h</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" s="22" t="n"/>
+    </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
@@ -2465,42 +3654,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>ماشین حالت Rtos — تسک‌ها</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>task_measurement: BspAdc_Init -&gt; Measurement_Init -&gt; retry Start هر 1s با check-in -&gt; loop osDelayUntil 1ms -&gt; Measurement_Run -&gt; check-in</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>task_control: Changeover_Init -&gt; McuPowerPath_Init -&gt; Charger_Init -&gt; Jitter_Init -&gt; Imbalance_Init -&gt; loop: snapshot zero -&gt; Fault_Evaluate -&gt; Jitter_Run -&gt; Charger_TechnicalFault -&gt; McuPowerPath_Run -&gt; Imbalance_Evaluate (prev state) -&gt; Changeover_Evaluate -&gt; Charger_Evaluate -&gt; PollKick -&gt; Delay</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>task_comm: EspLink_Init -&gt; loop: snapshot zero -&gt; Measurement_GetSnapshot -&gt; Fault_Get -&gt; EspLink_Run -&gt; check-in -&gt; Delay comm_period</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>task_ui: Ui_Init -&gt; BoardTest_Start -&gt; loop: snapshot zero -&gt; GetSnapshot -&gt; Ui_Tick -&gt; check-in -&gt; Delay UI_TICK_MS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>task_protection: loop: snapshot zero -&gt; GetSnapshot -&gt; Protection_Run -&gt; check-in -&gt; Delay protection_period</t>
         </is>

--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -145,6 +145,10 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -184,7 +188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -206,11 +210,12 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -314,6 +319,9 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -680,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +802,14 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t>62f3782</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
         </is>
       </c>
     </row>
@@ -952,7 +968,7 @@
       </c>
       <c r="J4" s="25" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="K4" s="25" t="inlineStr">
@@ -1041,7 +1057,7 @@
       </c>
       <c r="J5" s="27" t="inlineStr">
         <is>
-          <t>کار بی‌هنگ چندساعته = قبول؛ هر هنگ یا ریست = رد</t>
+          <t>باید ببینید: چند ساعت هیچ هنگ و ریستی نیست؛ چراغ‌ها، پنل و شارژ پیوسته و روان کار می‌کنند. اگر هنگ یا ریست دیدید، قبول نیست.</t>
         </is>
       </c>
       <c r="K5" s="27" t="n"/>
@@ -1058,10 +1074,9 @@
         </is>
       </c>
       <c r="P5" s="29" t="n"/>
-      <c r="Q5" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="Q5" s="31">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
@@ -1113,7 +1128,7 @@
       </c>
       <c r="J6" s="32" t="inlineStr">
         <is>
-          <t>رفتار درست هر دو کلید = قبول؛ برعکس یا بی‌اثر = رد</t>
+          <t>باید ببینید: هر دو کلید تمیز و بدون اثر اضافه کار می‌کنند؛ Enter تأیید و Esc لغو است. اگر برعکس یا بی‌اثر بودند، قبول نیست.</t>
         </is>
       </c>
       <c r="K6" s="32" t="n"/>
@@ -1130,10 +1145,9 @@
         </is>
       </c>
       <c r="P6" s="33" t="n"/>
-      <c r="Q6" s="35" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="Q6" s="35">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
@@ -1149,7 +1163,7 @@
       </c>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>پایین</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
@@ -1185,7 +1199,7 @@
       </c>
       <c r="J7" s="27" t="inlineStr">
         <is>
-          <t>نمایش نوبتی کامل = قبول؛ گم‌شدن پیام = رد</t>
+          <t>باید ببینید: پیام‌ها نوبتی و کامل نشان داده می‌شوند و هیچ‌کدام گم یا روی هم خراب نمی‌شوند. اگر پیامی گم شد، قبول نیست.</t>
         </is>
       </c>
       <c r="K7" s="27" t="n"/>
@@ -1202,896 +1216,775 @@
         </is>
       </c>
       <c r="P7" s="29" t="n"/>
-      <c r="Q7" s="31" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40.5" customHeight="1">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="22" t="n"/>
-      <c r="K8" s="22" t="n"/>
-      <c r="L8" s="22" t="n"/>
-      <c r="M8" s="22" t="n"/>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="22" t="n"/>
-      <c r="P8" s="22" t="n"/>
-      <c r="Q8" s="36">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+      <c r="Q7" s="31">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="22" t="n"/>
-      <c r="K9" s="22" t="n"/>
-      <c r="L9" s="22" t="n"/>
-      <c r="M9" s="22" t="n"/>
-      <c r="N9" s="22" t="n"/>
-      <c r="O9" s="22" t="n"/>
-      <c r="P9" s="22" t="n"/>
-      <c r="Q9" s="36">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="22" t="n"/>
-      <c r="M10" s="22" t="n"/>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="22" t="n"/>
-      <c r="P10" s="22" t="n"/>
-      <c r="Q10" s="36">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="40.5" customHeight="1">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="22" t="n"/>
-      <c r="J11" s="22" t="n"/>
-      <c r="K11" s="22" t="n"/>
-      <c r="L11" s="22" t="n"/>
-      <c r="M11" s="22" t="n"/>
-      <c r="N11" s="22" t="n"/>
-      <c r="O11" s="22" t="n"/>
-      <c r="P11" s="22" t="n"/>
-      <c r="Q11" s="36">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="22" t="n"/>
-      <c r="I12" s="22" t="n"/>
-      <c r="J12" s="22" t="n"/>
-      <c r="K12" s="22" t="n"/>
-      <c r="L12" s="22" t="n"/>
-      <c r="M12" s="22" t="n"/>
-      <c r="N12" s="22" t="n"/>
-      <c r="O12" s="22" t="n"/>
-      <c r="P12" s="22" t="n"/>
-      <c r="Q12" s="36">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="22" t="n"/>
-      <c r="H13" s="22" t="n"/>
-      <c r="I13" s="22" t="n"/>
-      <c r="J13" s="22" t="n"/>
-      <c r="K13" s="22" t="n"/>
-      <c r="L13" s="22" t="n"/>
-      <c r="M13" s="22" t="n"/>
-      <c r="N13" s="22" t="n"/>
-      <c r="O13" s="22" t="n"/>
-      <c r="P13" s="22" t="n"/>
-      <c r="Q13" s="36">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="22" t="n"/>
-      <c r="I14" s="22" t="n"/>
-      <c r="J14" s="22" t="n"/>
-      <c r="K14" s="22" t="n"/>
-      <c r="L14" s="22" t="n"/>
-      <c r="M14" s="22" t="n"/>
-      <c r="N14" s="22" t="n"/>
-      <c r="O14" s="22" t="n"/>
-      <c r="P14" s="22" t="n"/>
-      <c r="Q14" s="36">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="22" t="n"/>
-      <c r="F15" s="22" t="n"/>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="22" t="n"/>
-      <c r="I15" s="22" t="n"/>
-      <c r="J15" s="22" t="n"/>
-      <c r="K15" s="22" t="n"/>
-      <c r="L15" s="22" t="n"/>
-      <c r="M15" s="22" t="n"/>
-      <c r="N15" s="22" t="n"/>
-      <c r="O15" s="22" t="n"/>
-      <c r="P15" s="22" t="n"/>
-      <c r="Q15" s="36">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
-        <v/>
-      </c>
+    <row r="8">
+      <c r="A8" s="42" t="n"/>
+      <c r="B8" s="42" t="n"/>
+      <c r="C8" s="42" t="n"/>
+      <c r="D8" s="42" t="n"/>
+      <c r="E8" s="42" t="n"/>
+      <c r="F8" s="42" t="n"/>
+      <c r="G8" s="42" t="n"/>
+      <c r="H8" s="42" t="n"/>
+      <c r="I8" s="42" t="n"/>
+      <c r="J8" s="42" t="n"/>
+      <c r="K8" s="42" t="n"/>
+      <c r="L8" s="42" t="n"/>
+      <c r="M8" s="42" t="n"/>
+      <c r="N8" s="42" t="n"/>
+      <c r="O8" s="42" t="n"/>
+      <c r="P8" s="42" t="n"/>
+      <c r="Q8" s="43" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="n"/>
+      <c r="B9" s="42" t="n"/>
+      <c r="C9" s="42" t="n"/>
+      <c r="D9" s="42" t="n"/>
+      <c r="E9" s="42" t="n"/>
+      <c r="F9" s="42" t="n"/>
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="42" t="n"/>
+      <c r="I9" s="42" t="n"/>
+      <c r="J9" s="42" t="n"/>
+      <c r="K9" s="42" t="n"/>
+      <c r="L9" s="42" t="n"/>
+      <c r="M9" s="42" t="n"/>
+      <c r="N9" s="42" t="n"/>
+      <c r="O9" s="42" t="n"/>
+      <c r="P9" s="42" t="n"/>
+      <c r="Q9" s="43" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="n"/>
+      <c r="B10" s="42" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="42" t="n"/>
+      <c r="E10" s="42" t="n"/>
+      <c r="F10" s="42" t="n"/>
+      <c r="G10" s="42" t="n"/>
+      <c r="H10" s="42" t="n"/>
+      <c r="I10" s="42" t="n"/>
+      <c r="J10" s="42" t="n"/>
+      <c r="K10" s="42" t="n"/>
+      <c r="L10" s="42" t="n"/>
+      <c r="M10" s="42" t="n"/>
+      <c r="N10" s="42" t="n"/>
+      <c r="O10" s="42" t="n"/>
+      <c r="P10" s="42" t="n"/>
+      <c r="Q10" s="43" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="n"/>
+      <c r="B11" s="42" t="n"/>
+      <c r="C11" s="42" t="n"/>
+      <c r="D11" s="42" t="n"/>
+      <c r="E11" s="42" t="n"/>
+      <c r="F11" s="42" t="n"/>
+      <c r="G11" s="42" t="n"/>
+      <c r="H11" s="42" t="n"/>
+      <c r="I11" s="42" t="n"/>
+      <c r="J11" s="42" t="n"/>
+      <c r="K11" s="42" t="n"/>
+      <c r="L11" s="42" t="n"/>
+      <c r="M11" s="42" t="n"/>
+      <c r="N11" s="42" t="n"/>
+      <c r="O11" s="42" t="n"/>
+      <c r="P11" s="42" t="n"/>
+      <c r="Q11" s="43" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="n"/>
+      <c r="B12" s="42" t="n"/>
+      <c r="C12" s="42" t="n"/>
+      <c r="D12" s="42" t="n"/>
+      <c r="E12" s="42" t="n"/>
+      <c r="F12" s="42" t="n"/>
+      <c r="G12" s="42" t="n"/>
+      <c r="H12" s="42" t="n"/>
+      <c r="I12" s="42" t="n"/>
+      <c r="J12" s="42" t="n"/>
+      <c r="K12" s="42" t="n"/>
+      <c r="L12" s="42" t="n"/>
+      <c r="M12" s="42" t="n"/>
+      <c r="N12" s="42" t="n"/>
+      <c r="O12" s="42" t="n"/>
+      <c r="P12" s="42" t="n"/>
+      <c r="Q12" s="43" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="n"/>
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="42" t="n"/>
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="42" t="n"/>
+      <c r="F13" s="42" t="n"/>
+      <c r="G13" s="42" t="n"/>
+      <c r="H13" s="42" t="n"/>
+      <c r="I13" s="42" t="n"/>
+      <c r="J13" s="42" t="n"/>
+      <c r="K13" s="42" t="n"/>
+      <c r="L13" s="42" t="n"/>
+      <c r="M13" s="42" t="n"/>
+      <c r="N13" s="42" t="n"/>
+      <c r="O13" s="42" t="n"/>
+      <c r="P13" s="42" t="n"/>
+      <c r="Q13" s="43" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="n"/>
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="42" t="n"/>
+      <c r="E14" s="42" t="n"/>
+      <c r="F14" s="42" t="n"/>
+      <c r="G14" s="42" t="n"/>
+      <c r="H14" s="42" t="n"/>
+      <c r="I14" s="42" t="n"/>
+      <c r="J14" s="42" t="n"/>
+      <c r="K14" s="42" t="n"/>
+      <c r="L14" s="42" t="n"/>
+      <c r="M14" s="42" t="n"/>
+      <c r="N14" s="42" t="n"/>
+      <c r="O14" s="42" t="n"/>
+      <c r="P14" s="42" t="n"/>
+      <c r="Q14" s="43" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="n"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="42" t="n"/>
+      <c r="F15" s="42" t="n"/>
+      <c r="G15" s="42" t="n"/>
+      <c r="H15" s="42" t="n"/>
+      <c r="I15" s="42" t="n"/>
+      <c r="J15" s="42" t="n"/>
+      <c r="K15" s="42" t="n"/>
+      <c r="L15" s="42" t="n"/>
+      <c r="M15" s="42" t="n"/>
+      <c r="N15" s="42" t="n"/>
+      <c r="O15" s="42" t="n"/>
+      <c r="P15" s="42" t="n"/>
+      <c r="Q15" s="43" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
-      <c r="F16" s="22" t="n"/>
-      <c r="G16" s="22" t="n"/>
-      <c r="H16" s="22" t="n"/>
-      <c r="I16" s="22" t="n"/>
-      <c r="J16" s="22" t="n"/>
-      <c r="K16" s="22" t="n"/>
-      <c r="L16" s="22" t="n"/>
-      <c r="M16" s="22" t="n"/>
-      <c r="N16" s="22" t="n"/>
-      <c r="O16" s="22" t="n"/>
-      <c r="P16" s="22" t="n"/>
-      <c r="Q16" s="36">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
-        <v/>
-      </c>
+      <c r="A16" s="42" t="n"/>
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="42" t="n"/>
+      <c r="D16" s="42" t="n"/>
+      <c r="E16" s="42" t="n"/>
+      <c r="F16" s="42" t="n"/>
+      <c r="G16" s="42" t="n"/>
+      <c r="H16" s="42" t="n"/>
+      <c r="I16" s="42" t="n"/>
+      <c r="J16" s="42" t="n"/>
+      <c r="K16" s="42" t="n"/>
+      <c r="L16" s="42" t="n"/>
+      <c r="M16" s="42" t="n"/>
+      <c r="N16" s="42" t="n"/>
+      <c r="O16" s="42" t="n"/>
+      <c r="P16" s="42" t="n"/>
+      <c r="Q16" s="43" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="22" t="n"/>
-      <c r="H17" s="22" t="n"/>
-      <c r="I17" s="22" t="n"/>
-      <c r="J17" s="22" t="n"/>
-      <c r="K17" s="22" t="n"/>
-      <c r="L17" s="22" t="n"/>
-      <c r="M17" s="22" t="n"/>
-      <c r="N17" s="22" t="n"/>
-      <c r="O17" s="22" t="n"/>
-      <c r="P17" s="22" t="n"/>
-      <c r="Q17" s="36">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
-        <v/>
-      </c>
+      <c r="A17" s="42" t="n"/>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="42" t="n"/>
+      <c r="F17" s="42" t="n"/>
+      <c r="G17" s="42" t="n"/>
+      <c r="H17" s="42" t="n"/>
+      <c r="I17" s="42" t="n"/>
+      <c r="J17" s="42" t="n"/>
+      <c r="K17" s="42" t="n"/>
+      <c r="L17" s="42" t="n"/>
+      <c r="M17" s="42" t="n"/>
+      <c r="N17" s="42" t="n"/>
+      <c r="O17" s="42" t="n"/>
+      <c r="P17" s="42" t="n"/>
+      <c r="Q17" s="43" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="22" t="n"/>
-      <c r="K18" s="22" t="n"/>
-      <c r="L18" s="22" t="n"/>
-      <c r="M18" s="22" t="n"/>
-      <c r="N18" s="22" t="n"/>
-      <c r="O18" s="22" t="n"/>
-      <c r="P18" s="22" t="n"/>
-      <c r="Q18" s="36">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
-        <v/>
-      </c>
+      <c r="A18" s="42" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="42" t="n"/>
+      <c r="D18" s="42" t="n"/>
+      <c r="E18" s="42" t="n"/>
+      <c r="F18" s="42" t="n"/>
+      <c r="G18" s="42" t="n"/>
+      <c r="H18" s="42" t="n"/>
+      <c r="I18" s="42" t="n"/>
+      <c r="J18" s="42" t="n"/>
+      <c r="K18" s="42" t="n"/>
+      <c r="L18" s="42" t="n"/>
+      <c r="M18" s="42" t="n"/>
+      <c r="N18" s="42" t="n"/>
+      <c r="O18" s="42" t="n"/>
+      <c r="P18" s="42" t="n"/>
+      <c r="Q18" s="43" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="22" t="n"/>
-      <c r="M19" s="22" t="n"/>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="36">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
-        <v/>
-      </c>
+      <c r="A19" s="42" t="n"/>
+      <c r="B19" s="42" t="n"/>
+      <c r="C19" s="42" t="n"/>
+      <c r="D19" s="42" t="n"/>
+      <c r="E19" s="42" t="n"/>
+      <c r="F19" s="42" t="n"/>
+      <c r="G19" s="42" t="n"/>
+      <c r="H19" s="42" t="n"/>
+      <c r="I19" s="42" t="n"/>
+      <c r="J19" s="42" t="n"/>
+      <c r="K19" s="42" t="n"/>
+      <c r="L19" s="42" t="n"/>
+      <c r="M19" s="42" t="n"/>
+      <c r="N19" s="42" t="n"/>
+      <c r="O19" s="42" t="n"/>
+      <c r="P19" s="42" t="n"/>
+      <c r="Q19" s="43" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n"/>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="22" t="n"/>
-      <c r="M20" s="22" t="n"/>
-      <c r="N20" s="22" t="n"/>
-      <c r="O20" s="22" t="n"/>
-      <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="36">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
-        <v/>
-      </c>
+      <c r="A20" s="42" t="n"/>
+      <c r="B20" s="42" t="n"/>
+      <c r="C20" s="42" t="n"/>
+      <c r="D20" s="42" t="n"/>
+      <c r="E20" s="42" t="n"/>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="42" t="n"/>
+      <c r="H20" s="42" t="n"/>
+      <c r="I20" s="42" t="n"/>
+      <c r="J20" s="42" t="n"/>
+      <c r="K20" s="42" t="n"/>
+      <c r="L20" s="42" t="n"/>
+      <c r="M20" s="42" t="n"/>
+      <c r="N20" s="42" t="n"/>
+      <c r="O20" s="42" t="n"/>
+      <c r="P20" s="42" t="n"/>
+      <c r="Q20" s="43" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="n"/>
-      <c r="K21" s="22" t="n"/>
-      <c r="L21" s="22" t="n"/>
-      <c r="M21" s="22" t="n"/>
-      <c r="N21" s="22" t="n"/>
-      <c r="O21" s="22" t="n"/>
-      <c r="P21" s="22" t="n"/>
-      <c r="Q21" s="36">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
-        <v/>
-      </c>
+      <c r="A21" s="42" t="n"/>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="42" t="n"/>
+      <c r="D21" s="42" t="n"/>
+      <c r="E21" s="42" t="n"/>
+      <c r="F21" s="42" t="n"/>
+      <c r="G21" s="42" t="n"/>
+      <c r="H21" s="42" t="n"/>
+      <c r="I21" s="42" t="n"/>
+      <c r="J21" s="42" t="n"/>
+      <c r="K21" s="42" t="n"/>
+      <c r="L21" s="42" t="n"/>
+      <c r="M21" s="42" t="n"/>
+      <c r="N21" s="42" t="n"/>
+      <c r="O21" s="42" t="n"/>
+      <c r="P21" s="42" t="n"/>
+      <c r="Q21" s="43" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="n"/>
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="22" t="n"/>
-      <c r="F22" s="22" t="n"/>
-      <c r="G22" s="22" t="n"/>
-      <c r="H22" s="22" t="n"/>
-      <c r="I22" s="22" t="n"/>
-      <c r="J22" s="22" t="n"/>
-      <c r="K22" s="22" t="n"/>
-      <c r="L22" s="22" t="n"/>
-      <c r="M22" s="22" t="n"/>
-      <c r="N22" s="22" t="n"/>
-      <c r="O22" s="22" t="n"/>
-      <c r="P22" s="22" t="n"/>
-      <c r="Q22" s="36">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
-        <v/>
-      </c>
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="42" t="n"/>
+      <c r="H22" s="42" t="n"/>
+      <c r="I22" s="42" t="n"/>
+      <c r="J22" s="42" t="n"/>
+      <c r="K22" s="42" t="n"/>
+      <c r="L22" s="42" t="n"/>
+      <c r="M22" s="42" t="n"/>
+      <c r="N22" s="42" t="n"/>
+      <c r="O22" s="42" t="n"/>
+      <c r="P22" s="42" t="n"/>
+      <c r="Q22" s="43" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="n"/>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="22" t="n"/>
-      <c r="F23" s="22" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="22" t="n"/>
-      <c r="I23" s="22" t="n"/>
-      <c r="J23" s="22" t="n"/>
-      <c r="K23" s="22" t="n"/>
-      <c r="L23" s="22" t="n"/>
-      <c r="M23" s="22" t="n"/>
-      <c r="N23" s="22" t="n"/>
-      <c r="O23" s="22" t="n"/>
-      <c r="P23" s="22" t="n"/>
-      <c r="Q23" s="36">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
+      <c r="A23" s="42" t="n"/>
+      <c r="B23" s="42" t="n"/>
+      <c r="C23" s="42" t="n"/>
+      <c r="D23" s="42" t="n"/>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="42" t="n"/>
+      <c r="H23" s="42" t="n"/>
+      <c r="I23" s="42" t="n"/>
+      <c r="J23" s="42" t="n"/>
+      <c r="K23" s="42" t="n"/>
+      <c r="L23" s="42" t="n"/>
+      <c r="M23" s="42" t="n"/>
+      <c r="N23" s="42" t="n"/>
+      <c r="O23" s="42" t="n"/>
+      <c r="P23" s="42" t="n"/>
+      <c r="Q23" s="43" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="n"/>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="22" t="n"/>
-      <c r="I24" s="22" t="n"/>
-      <c r="J24" s="22" t="n"/>
-      <c r="K24" s="22" t="n"/>
-      <c r="L24" s="22" t="n"/>
-      <c r="M24" s="22" t="n"/>
-      <c r="N24" s="22" t="n"/>
-      <c r="O24" s="22" t="n"/>
-      <c r="P24" s="22" t="n"/>
-      <c r="Q24" s="36">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
+      <c r="A24" s="42" t="n"/>
+      <c r="B24" s="42" t="n"/>
+      <c r="C24" s="42" t="n"/>
+      <c r="D24" s="42" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="42" t="n"/>
+      <c r="G24" s="42" t="n"/>
+      <c r="H24" s="42" t="n"/>
+      <c r="I24" s="42" t="n"/>
+      <c r="J24" s="42" t="n"/>
+      <c r="K24" s="42" t="n"/>
+      <c r="L24" s="42" t="n"/>
+      <c r="M24" s="42" t="n"/>
+      <c r="N24" s="42" t="n"/>
+      <c r="O24" s="42" t="n"/>
+      <c r="P24" s="42" t="n"/>
+      <c r="Q24" s="43" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="n"/>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="22" t="n"/>
-      <c r="I25" s="22" t="n"/>
-      <c r="J25" s="22" t="n"/>
-      <c r="K25" s="22" t="n"/>
-      <c r="L25" s="22" t="n"/>
-      <c r="M25" s="22" t="n"/>
-      <c r="N25" s="22" t="n"/>
-      <c r="O25" s="22" t="n"/>
-      <c r="P25" s="22" t="n"/>
-      <c r="Q25" s="36">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
-        <v/>
-      </c>
+      <c r="A25" s="42" t="n"/>
+      <c r="B25" s="42" t="n"/>
+      <c r="C25" s="42" t="n"/>
+      <c r="D25" s="42" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="F25" s="42" t="n"/>
+      <c r="G25" s="42" t="n"/>
+      <c r="H25" s="42" t="n"/>
+      <c r="I25" s="42" t="n"/>
+      <c r="J25" s="42" t="n"/>
+      <c r="K25" s="42" t="n"/>
+      <c r="L25" s="42" t="n"/>
+      <c r="M25" s="42" t="n"/>
+      <c r="N25" s="42" t="n"/>
+      <c r="O25" s="42" t="n"/>
+      <c r="P25" s="42" t="n"/>
+      <c r="Q25" s="43" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="n"/>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
-      <c r="G26" s="22" t="n"/>
-      <c r="H26" s="22" t="n"/>
-      <c r="I26" s="22" t="n"/>
-      <c r="J26" s="22" t="n"/>
-      <c r="K26" s="22" t="n"/>
-      <c r="L26" s="22" t="n"/>
-      <c r="M26" s="22" t="n"/>
-      <c r="N26" s="22" t="n"/>
-      <c r="O26" s="22" t="n"/>
-      <c r="P26" s="22" t="n"/>
-      <c r="Q26" s="36">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
-        <v/>
-      </c>
+      <c r="A26" s="42" t="n"/>
+      <c r="B26" s="42" t="n"/>
+      <c r="C26" s="42" t="n"/>
+      <c r="D26" s="42" t="n"/>
+      <c r="E26" s="42" t="n"/>
+      <c r="F26" s="42" t="n"/>
+      <c r="G26" s="42" t="n"/>
+      <c r="H26" s="42" t="n"/>
+      <c r="I26" s="42" t="n"/>
+      <c r="J26" s="42" t="n"/>
+      <c r="K26" s="42" t="n"/>
+      <c r="L26" s="42" t="n"/>
+      <c r="M26" s="42" t="n"/>
+      <c r="N26" s="42" t="n"/>
+      <c r="O26" s="42" t="n"/>
+      <c r="P26" s="42" t="n"/>
+      <c r="Q26" s="43" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="n"/>
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
-      <c r="G27" s="22" t="n"/>
-      <c r="H27" s="22" t="n"/>
-      <c r="I27" s="22" t="n"/>
-      <c r="J27" s="22" t="n"/>
-      <c r="K27" s="22" t="n"/>
-      <c r="L27" s="22" t="n"/>
-      <c r="M27" s="22" t="n"/>
-      <c r="N27" s="22" t="n"/>
-      <c r="O27" s="22" t="n"/>
-      <c r="P27" s="22" t="n"/>
-      <c r="Q27" s="36">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
+      <c r="A27" s="42" t="n"/>
+      <c r="B27" s="42" t="n"/>
+      <c r="C27" s="42" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="F27" s="42" t="n"/>
+      <c r="G27" s="42" t="n"/>
+      <c r="H27" s="42" t="n"/>
+      <c r="I27" s="42" t="n"/>
+      <c r="J27" s="42" t="n"/>
+      <c r="K27" s="42" t="n"/>
+      <c r="L27" s="42" t="n"/>
+      <c r="M27" s="42" t="n"/>
+      <c r="N27" s="42" t="n"/>
+      <c r="O27" s="42" t="n"/>
+      <c r="P27" s="42" t="n"/>
+      <c r="Q27" s="43" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="n"/>
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="22" t="n"/>
-      <c r="F28" s="22" t="n"/>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="22" t="n"/>
-      <c r="I28" s="22" t="n"/>
-      <c r="J28" s="22" t="n"/>
-      <c r="K28" s="22" t="n"/>
-      <c r="L28" s="22" t="n"/>
-      <c r="M28" s="22" t="n"/>
-      <c r="N28" s="22" t="n"/>
-      <c r="O28" s="22" t="n"/>
-      <c r="P28" s="22" t="n"/>
-      <c r="Q28" s="36">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
+      <c r="A28" s="42" t="n"/>
+      <c r="B28" s="42" t="n"/>
+      <c r="C28" s="42" t="n"/>
+      <c r="D28" s="42" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="F28" s="42" t="n"/>
+      <c r="G28" s="42" t="n"/>
+      <c r="H28" s="42" t="n"/>
+      <c r="I28" s="42" t="n"/>
+      <c r="J28" s="42" t="n"/>
+      <c r="K28" s="42" t="n"/>
+      <c r="L28" s="42" t="n"/>
+      <c r="M28" s="42" t="n"/>
+      <c r="N28" s="42" t="n"/>
+      <c r="O28" s="42" t="n"/>
+      <c r="P28" s="42" t="n"/>
+      <c r="Q28" s="43" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="n"/>
-      <c r="B29" s="22" t="n"/>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="22" t="n"/>
-      <c r="E29" s="22" t="n"/>
-      <c r="F29" s="22" t="n"/>
-      <c r="G29" s="22" t="n"/>
-      <c r="H29" s="22" t="n"/>
-      <c r="I29" s="22" t="n"/>
-      <c r="J29" s="22" t="n"/>
-      <c r="K29" s="22" t="n"/>
-      <c r="L29" s="22" t="n"/>
-      <c r="M29" s="22" t="n"/>
-      <c r="N29" s="22" t="n"/>
-      <c r="O29" s="22" t="n"/>
-      <c r="P29" s="22" t="n"/>
-      <c r="Q29" s="36">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
+      <c r="A29" s="42" t="n"/>
+      <c r="B29" s="42" t="n"/>
+      <c r="C29" s="42" t="n"/>
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="42" t="n"/>
+      <c r="F29" s="42" t="n"/>
+      <c r="G29" s="42" t="n"/>
+      <c r="H29" s="42" t="n"/>
+      <c r="I29" s="42" t="n"/>
+      <c r="J29" s="42" t="n"/>
+      <c r="K29" s="42" t="n"/>
+      <c r="L29" s="42" t="n"/>
+      <c r="M29" s="42" t="n"/>
+      <c r="N29" s="42" t="n"/>
+      <c r="O29" s="42" t="n"/>
+      <c r="P29" s="42" t="n"/>
+      <c r="Q29" s="43" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="n"/>
-      <c r="B30" s="22" t="n"/>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="22" t="n"/>
-      <c r="E30" s="22" t="n"/>
-      <c r="F30" s="22" t="n"/>
-      <c r="G30" s="22" t="n"/>
-      <c r="H30" s="22" t="n"/>
-      <c r="I30" s="22" t="n"/>
-      <c r="J30" s="22" t="n"/>
-      <c r="K30" s="22" t="n"/>
-      <c r="L30" s="22" t="n"/>
-      <c r="M30" s="22" t="n"/>
-      <c r="N30" s="22" t="n"/>
-      <c r="O30" s="22" t="n"/>
-      <c r="P30" s="22" t="n"/>
-      <c r="Q30" s="36">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
+      <c r="A30" s="42" t="n"/>
+      <c r="B30" s="42" t="n"/>
+      <c r="C30" s="42" t="n"/>
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="42" t="n"/>
+      <c r="F30" s="42" t="n"/>
+      <c r="G30" s="42" t="n"/>
+      <c r="H30" s="42" t="n"/>
+      <c r="I30" s="42" t="n"/>
+      <c r="J30" s="42" t="n"/>
+      <c r="K30" s="42" t="n"/>
+      <c r="L30" s="42" t="n"/>
+      <c r="M30" s="42" t="n"/>
+      <c r="N30" s="42" t="n"/>
+      <c r="O30" s="42" t="n"/>
+      <c r="P30" s="42" t="n"/>
+      <c r="Q30" s="43" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="22" t="n"/>
-      <c r="F31" s="22" t="n"/>
-      <c r="G31" s="22" t="n"/>
-      <c r="H31" s="22" t="n"/>
-      <c r="I31" s="22" t="n"/>
-      <c r="J31" s="22" t="n"/>
-      <c r="K31" s="22" t="n"/>
-      <c r="L31" s="22" t="n"/>
-      <c r="M31" s="22" t="n"/>
-      <c r="N31" s="22" t="n"/>
-      <c r="O31" s="22" t="n"/>
-      <c r="P31" s="22" t="n"/>
-      <c r="Q31" s="36">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
+      <c r="A31" s="42" t="n"/>
+      <c r="B31" s="42" t="n"/>
+      <c r="C31" s="42" t="n"/>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="42" t="n"/>
+      <c r="G31" s="42" t="n"/>
+      <c r="H31" s="42" t="n"/>
+      <c r="I31" s="42" t="n"/>
+      <c r="J31" s="42" t="n"/>
+      <c r="K31" s="42" t="n"/>
+      <c r="L31" s="42" t="n"/>
+      <c r="M31" s="42" t="n"/>
+      <c r="N31" s="42" t="n"/>
+      <c r="O31" s="42" t="n"/>
+      <c r="P31" s="42" t="n"/>
+      <c r="Q31" s="43" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="22" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="F32" s="22" t="n"/>
-      <c r="G32" s="22" t="n"/>
-      <c r="H32" s="22" t="n"/>
-      <c r="I32" s="22" t="n"/>
-      <c r="J32" s="22" t="n"/>
-      <c r="K32" s="22" t="n"/>
-      <c r="L32" s="22" t="n"/>
-      <c r="M32" s="22" t="n"/>
-      <c r="N32" s="22" t="n"/>
-      <c r="O32" s="22" t="n"/>
-      <c r="P32" s="22" t="n"/>
-      <c r="Q32" s="36">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
+      <c r="A32" s="42" t="n"/>
+      <c r="B32" s="42" t="n"/>
+      <c r="C32" s="42" t="n"/>
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="42" t="n"/>
+      <c r="G32" s="42" t="n"/>
+      <c r="H32" s="42" t="n"/>
+      <c r="I32" s="42" t="n"/>
+      <c r="J32" s="42" t="n"/>
+      <c r="K32" s="42" t="n"/>
+      <c r="L32" s="42" t="n"/>
+      <c r="M32" s="42" t="n"/>
+      <c r="N32" s="42" t="n"/>
+      <c r="O32" s="42" t="n"/>
+      <c r="P32" s="42" t="n"/>
+      <c r="Q32" s="43" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="n"/>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
-      <c r="F33" s="22" t="n"/>
-      <c r="G33" s="22" t="n"/>
-      <c r="H33" s="22" t="n"/>
-      <c r="I33" s="22" t="n"/>
-      <c r="J33" s="22" t="n"/>
-      <c r="K33" s="22" t="n"/>
-      <c r="L33" s="22" t="n"/>
-      <c r="M33" s="22" t="n"/>
-      <c r="N33" s="22" t="n"/>
-      <c r="O33" s="22" t="n"/>
-      <c r="P33" s="22" t="n"/>
-      <c r="Q33" s="36">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
+      <c r="A33" s="42" t="n"/>
+      <c r="B33" s="42" t="n"/>
+      <c r="C33" s="42" t="n"/>
+      <c r="D33" s="42" t="n"/>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="42" t="n"/>
+      <c r="G33" s="42" t="n"/>
+      <c r="H33" s="42" t="n"/>
+      <c r="I33" s="42" t="n"/>
+      <c r="J33" s="42" t="n"/>
+      <c r="K33" s="42" t="n"/>
+      <c r="L33" s="42" t="n"/>
+      <c r="M33" s="42" t="n"/>
+      <c r="N33" s="42" t="n"/>
+      <c r="O33" s="42" t="n"/>
+      <c r="P33" s="42" t="n"/>
+      <c r="Q33" s="43" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="n"/>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="22" t="n"/>
-      <c r="H34" s="22" t="n"/>
-      <c r="I34" s="22" t="n"/>
-      <c r="J34" s="22" t="n"/>
-      <c r="K34" s="22" t="n"/>
-      <c r="L34" s="22" t="n"/>
-      <c r="M34" s="22" t="n"/>
-      <c r="N34" s="22" t="n"/>
-      <c r="O34" s="22" t="n"/>
-      <c r="P34" s="22" t="n"/>
-      <c r="Q34" s="36">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
+      <c r="A34" s="42" t="n"/>
+      <c r="B34" s="42" t="n"/>
+      <c r="C34" s="42" t="n"/>
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="42" t="n"/>
+      <c r="G34" s="42" t="n"/>
+      <c r="H34" s="42" t="n"/>
+      <c r="I34" s="42" t="n"/>
+      <c r="J34" s="42" t="n"/>
+      <c r="K34" s="42" t="n"/>
+      <c r="L34" s="42" t="n"/>
+      <c r="M34" s="42" t="n"/>
+      <c r="N34" s="42" t="n"/>
+      <c r="O34" s="42" t="n"/>
+      <c r="P34" s="42" t="n"/>
+      <c r="Q34" s="43" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="n"/>
-      <c r="B35" s="22" t="n"/>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="22" t="n"/>
-      <c r="F35" s="22" t="n"/>
-      <c r="G35" s="22" t="n"/>
-      <c r="H35" s="22" t="n"/>
-      <c r="I35" s="22" t="n"/>
-      <c r="J35" s="22" t="n"/>
-      <c r="K35" s="22" t="n"/>
-      <c r="L35" s="22" t="n"/>
-      <c r="M35" s="22" t="n"/>
-      <c r="N35" s="22" t="n"/>
-      <c r="O35" s="22" t="n"/>
-      <c r="P35" s="22" t="n"/>
-      <c r="Q35" s="36">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
+      <c r="A35" s="42" t="n"/>
+      <c r="B35" s="42" t="n"/>
+      <c r="C35" s="42" t="n"/>
+      <c r="D35" s="42" t="n"/>
+      <c r="E35" s="42" t="n"/>
+      <c r="F35" s="42" t="n"/>
+      <c r="G35" s="42" t="n"/>
+      <c r="H35" s="42" t="n"/>
+      <c r="I35" s="42" t="n"/>
+      <c r="J35" s="42" t="n"/>
+      <c r="K35" s="42" t="n"/>
+      <c r="L35" s="42" t="n"/>
+      <c r="M35" s="42" t="n"/>
+      <c r="N35" s="42" t="n"/>
+      <c r="O35" s="42" t="n"/>
+      <c r="P35" s="42" t="n"/>
+      <c r="Q35" s="43" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="n"/>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="22" t="n"/>
-      <c r="G36" s="22" t="n"/>
-      <c r="H36" s="22" t="n"/>
-      <c r="I36" s="22" t="n"/>
-      <c r="J36" s="22" t="n"/>
-      <c r="K36" s="22" t="n"/>
-      <c r="L36" s="22" t="n"/>
-      <c r="M36" s="22" t="n"/>
-      <c r="N36" s="22" t="n"/>
-      <c r="O36" s="22" t="n"/>
-      <c r="P36" s="22" t="n"/>
-      <c r="Q36" s="36">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
+      <c r="A36" s="42" t="n"/>
+      <c r="B36" s="42" t="n"/>
+      <c r="C36" s="42" t="n"/>
+      <c r="D36" s="42" t="n"/>
+      <c r="E36" s="42" t="n"/>
+      <c r="F36" s="42" t="n"/>
+      <c r="G36" s="42" t="n"/>
+      <c r="H36" s="42" t="n"/>
+      <c r="I36" s="42" t="n"/>
+      <c r="J36" s="42" t="n"/>
+      <c r="K36" s="42" t="n"/>
+      <c r="L36" s="42" t="n"/>
+      <c r="M36" s="42" t="n"/>
+      <c r="N36" s="42" t="n"/>
+      <c r="O36" s="42" t="n"/>
+      <c r="P36" s="42" t="n"/>
+      <c r="Q36" s="43" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="n"/>
-      <c r="B37" s="22" t="n"/>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="22" t="n"/>
-      <c r="F37" s="22" t="n"/>
-      <c r="G37" s="22" t="n"/>
-      <c r="H37" s="22" t="n"/>
-      <c r="I37" s="22" t="n"/>
-      <c r="J37" s="22" t="n"/>
-      <c r="K37" s="22" t="n"/>
-      <c r="L37" s="22" t="n"/>
-      <c r="M37" s="22" t="n"/>
-      <c r="N37" s="22" t="n"/>
-      <c r="O37" s="22" t="n"/>
-      <c r="P37" s="22" t="n"/>
-      <c r="Q37" s="36">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
+      <c r="A37" s="42" t="n"/>
+      <c r="B37" s="42" t="n"/>
+      <c r="C37" s="42" t="n"/>
+      <c r="D37" s="42" t="n"/>
+      <c r="E37" s="42" t="n"/>
+      <c r="F37" s="42" t="n"/>
+      <c r="G37" s="42" t="n"/>
+      <c r="H37" s="42" t="n"/>
+      <c r="I37" s="42" t="n"/>
+      <c r="J37" s="42" t="n"/>
+      <c r="K37" s="42" t="n"/>
+      <c r="L37" s="42" t="n"/>
+      <c r="M37" s="42" t="n"/>
+      <c r="N37" s="42" t="n"/>
+      <c r="O37" s="42" t="n"/>
+      <c r="P37" s="42" t="n"/>
+      <c r="Q37" s="43" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="n"/>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="22" t="n"/>
-      <c r="I38" s="22" t="n"/>
-      <c r="J38" s="22" t="n"/>
-      <c r="K38" s="22" t="n"/>
-      <c r="L38" s="22" t="n"/>
-      <c r="M38" s="22" t="n"/>
-      <c r="N38" s="22" t="n"/>
-      <c r="O38" s="22" t="n"/>
-      <c r="P38" s="22" t="n"/>
-      <c r="Q38" s="36">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
+      <c r="A38" s="42" t="n"/>
+      <c r="B38" s="42" t="n"/>
+      <c r="C38" s="42" t="n"/>
+      <c r="D38" s="42" t="n"/>
+      <c r="E38" s="42" t="n"/>
+      <c r="F38" s="42" t="n"/>
+      <c r="G38" s="42" t="n"/>
+      <c r="H38" s="42" t="n"/>
+      <c r="I38" s="42" t="n"/>
+      <c r="J38" s="42" t="n"/>
+      <c r="K38" s="42" t="n"/>
+      <c r="L38" s="42" t="n"/>
+      <c r="M38" s="42" t="n"/>
+      <c r="N38" s="42" t="n"/>
+      <c r="O38" s="42" t="n"/>
+      <c r="P38" s="42" t="n"/>
+      <c r="Q38" s="43" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="n"/>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="22" t="n"/>
-      <c r="H39" s="22" t="n"/>
-      <c r="I39" s="22" t="n"/>
-      <c r="J39" s="22" t="n"/>
-      <c r="K39" s="22" t="n"/>
-      <c r="L39" s="22" t="n"/>
-      <c r="M39" s="22" t="n"/>
-      <c r="N39" s="22" t="n"/>
-      <c r="O39" s="22" t="n"/>
-      <c r="P39" s="22" t="n"/>
-      <c r="Q39" s="36">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
+      <c r="A39" s="42" t="n"/>
+      <c r="B39" s="42" t="n"/>
+      <c r="C39" s="42" t="n"/>
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="42" t="n"/>
+      <c r="F39" s="42" t="n"/>
+      <c r="G39" s="42" t="n"/>
+      <c r="H39" s="42" t="n"/>
+      <c r="I39" s="42" t="n"/>
+      <c r="J39" s="42" t="n"/>
+      <c r="K39" s="42" t="n"/>
+      <c r="L39" s="42" t="n"/>
+      <c r="M39" s="42" t="n"/>
+      <c r="N39" s="42" t="n"/>
+      <c r="O39" s="42" t="n"/>
+      <c r="P39" s="42" t="n"/>
+      <c r="Q39" s="43" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="n"/>
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n"/>
-      <c r="F40" s="22" t="n"/>
-      <c r="G40" s="22" t="n"/>
-      <c r="H40" s="22" t="n"/>
-      <c r="I40" s="22" t="n"/>
-      <c r="J40" s="22" t="n"/>
-      <c r="K40" s="22" t="n"/>
-      <c r="L40" s="22" t="n"/>
-      <c r="M40" s="22" t="n"/>
-      <c r="N40" s="22" t="n"/>
-      <c r="O40" s="22" t="n"/>
-      <c r="P40" s="22" t="n"/>
-      <c r="Q40" s="36">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
+      <c r="A40" s="42" t="n"/>
+      <c r="B40" s="42" t="n"/>
+      <c r="C40" s="42" t="n"/>
+      <c r="D40" s="42" t="n"/>
+      <c r="E40" s="42" t="n"/>
+      <c r="F40" s="42" t="n"/>
+      <c r="G40" s="42" t="n"/>
+      <c r="H40" s="42" t="n"/>
+      <c r="I40" s="42" t="n"/>
+      <c r="J40" s="42" t="n"/>
+      <c r="K40" s="42" t="n"/>
+      <c r="L40" s="42" t="n"/>
+      <c r="M40" s="42" t="n"/>
+      <c r="N40" s="42" t="n"/>
+      <c r="O40" s="42" t="n"/>
+      <c r="P40" s="42" t="n"/>
+      <c r="Q40" s="43" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="n"/>
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="22" t="n"/>
-      <c r="F41" s="22" t="n"/>
-      <c r="G41" s="22" t="n"/>
-      <c r="H41" s="22" t="n"/>
-      <c r="I41" s="22" t="n"/>
-      <c r="J41" s="22" t="n"/>
-      <c r="K41" s="22" t="n"/>
-      <c r="L41" s="22" t="n"/>
-      <c r="M41" s="22" t="n"/>
-      <c r="N41" s="22" t="n"/>
-      <c r="O41" s="22" t="n"/>
-      <c r="P41" s="22" t="n"/>
-      <c r="Q41" s="36">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
+      <c r="A41" s="42" t="n"/>
+      <c r="B41" s="42" t="n"/>
+      <c r="C41" s="42" t="n"/>
+      <c r="D41" s="42" t="n"/>
+      <c r="E41" s="42" t="n"/>
+      <c r="F41" s="42" t="n"/>
+      <c r="G41" s="42" t="n"/>
+      <c r="H41" s="42" t="n"/>
+      <c r="I41" s="42" t="n"/>
+      <c r="J41" s="42" t="n"/>
+      <c r="K41" s="42" t="n"/>
+      <c r="L41" s="42" t="n"/>
+      <c r="M41" s="42" t="n"/>
+      <c r="N41" s="42" t="n"/>
+      <c r="O41" s="42" t="n"/>
+      <c r="P41" s="42" t="n"/>
+      <c r="Q41" s="43" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="n"/>
-      <c r="B42" s="22" t="n"/>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="22" t="n"/>
-      <c r="F42" s="22" t="n"/>
-      <c r="G42" s="22" t="n"/>
-      <c r="H42" s="22" t="n"/>
-      <c r="I42" s="22" t="n"/>
-      <c r="J42" s="22" t="n"/>
-      <c r="K42" s="22" t="n"/>
-      <c r="L42" s="22" t="n"/>
-      <c r="M42" s="22" t="n"/>
-      <c r="N42" s="22" t="n"/>
-      <c r="O42" s="22" t="n"/>
-      <c r="P42" s="22" t="n"/>
-      <c r="Q42" s="36">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
+      <c r="A42" s="42" t="n"/>
+      <c r="B42" s="42" t="n"/>
+      <c r="C42" s="42" t="n"/>
+      <c r="D42" s="42" t="n"/>
+      <c r="E42" s="42" t="n"/>
+      <c r="F42" s="42" t="n"/>
+      <c r="G42" s="42" t="n"/>
+      <c r="H42" s="42" t="n"/>
+      <c r="I42" s="42" t="n"/>
+      <c r="J42" s="42" t="n"/>
+      <c r="K42" s="42" t="n"/>
+      <c r="L42" s="42" t="n"/>
+      <c r="M42" s="42" t="n"/>
+      <c r="N42" s="42" t="n"/>
+      <c r="O42" s="42" t="n"/>
+      <c r="P42" s="42" t="n"/>
+      <c r="Q42" s="43" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="n"/>
-      <c r="B43" s="22" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="22" t="n"/>
-      <c r="F43" s="22" t="n"/>
-      <c r="G43" s="22" t="n"/>
-      <c r="H43" s="22" t="n"/>
-      <c r="I43" s="22" t="n"/>
-      <c r="J43" s="22" t="n"/>
-      <c r="K43" s="22" t="n"/>
-      <c r="L43" s="22" t="n"/>
-      <c r="M43" s="22" t="n"/>
-      <c r="N43" s="22" t="n"/>
-      <c r="O43" s="22" t="n"/>
-      <c r="P43" s="22" t="n"/>
-      <c r="Q43" s="36">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
+      <c r="A43" s="42" t="n"/>
+      <c r="B43" s="42" t="n"/>
+      <c r="C43" s="42" t="n"/>
+      <c r="D43" s="42" t="n"/>
+      <c r="E43" s="42" t="n"/>
+      <c r="F43" s="42" t="n"/>
+      <c r="G43" s="42" t="n"/>
+      <c r="H43" s="42" t="n"/>
+      <c r="I43" s="42" t="n"/>
+      <c r="J43" s="42" t="n"/>
+      <c r="K43" s="42" t="n"/>
+      <c r="L43" s="42" t="n"/>
+      <c r="M43" s="42" t="n"/>
+      <c r="N43" s="42" t="n"/>
+      <c r="O43" s="42" t="n"/>
+      <c r="P43" s="42" t="n"/>
+      <c r="Q43" s="43" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="n"/>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="22" t="n"/>
-      <c r="F44" s="22" t="n"/>
-      <c r="G44" s="22" t="n"/>
-      <c r="H44" s="22" t="n"/>
-      <c r="I44" s="22" t="n"/>
-      <c r="J44" s="22" t="n"/>
-      <c r="K44" s="22" t="n"/>
-      <c r="L44" s="22" t="n"/>
-      <c r="M44" s="22" t="n"/>
-      <c r="N44" s="22" t="n"/>
-      <c r="O44" s="22" t="n"/>
-      <c r="P44" s="22" t="n"/>
-      <c r="Q44" s="36">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
+      <c r="A44" s="42" t="n"/>
+      <c r="B44" s="42" t="n"/>
+      <c r="C44" s="42" t="n"/>
+      <c r="D44" s="42" t="n"/>
+      <c r="E44" s="42" t="n"/>
+      <c r="F44" s="42" t="n"/>
+      <c r="G44" s="42" t="n"/>
+      <c r="H44" s="42" t="n"/>
+      <c r="I44" s="42" t="n"/>
+      <c r="J44" s="42" t="n"/>
+      <c r="K44" s="42" t="n"/>
+      <c r="L44" s="42" t="n"/>
+      <c r="M44" s="42" t="n"/>
+      <c r="N44" s="42" t="n"/>
+      <c r="O44" s="42" t="n"/>
+      <c r="P44" s="42" t="n"/>
+      <c r="Q44" s="43" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="n"/>
-      <c r="B45" s="22" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="22" t="n"/>
-      <c r="F45" s="22" t="n"/>
-      <c r="G45" s="22" t="n"/>
-      <c r="H45" s="22" t="n"/>
-      <c r="I45" s="22" t="n"/>
-      <c r="J45" s="22" t="n"/>
-      <c r="K45" s="22" t="n"/>
-      <c r="L45" s="22" t="n"/>
-      <c r="M45" s="22" t="n"/>
-      <c r="N45" s="22" t="n"/>
-      <c r="O45" s="22" t="n"/>
-      <c r="P45" s="22" t="n"/>
-      <c r="Q45" s="36">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
+      <c r="A45" s="42" t="n"/>
+      <c r="B45" s="42" t="n"/>
+      <c r="C45" s="42" t="n"/>
+      <c r="D45" s="42" t="n"/>
+      <c r="E45" s="42" t="n"/>
+      <c r="F45" s="42" t="n"/>
+      <c r="G45" s="42" t="n"/>
+      <c r="H45" s="42" t="n"/>
+      <c r="I45" s="42" t="n"/>
+      <c r="J45" s="42" t="n"/>
+      <c r="K45" s="42" t="n"/>
+      <c r="L45" s="42" t="n"/>
+      <c r="M45" s="42" t="n"/>
+      <c r="N45" s="42" t="n"/>
+      <c r="O45" s="42" t="n"/>
+      <c r="P45" s="42" t="n"/>
+      <c r="Q45" s="43" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="n"/>
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="22" t="n"/>
-      <c r="F46" s="22" t="n"/>
-      <c r="G46" s="22" t="n"/>
-      <c r="H46" s="22" t="n"/>
-      <c r="I46" s="22" t="n"/>
-      <c r="J46" s="22" t="n"/>
-      <c r="K46" s="22" t="n"/>
-      <c r="L46" s="22" t="n"/>
-      <c r="M46" s="22" t="n"/>
-      <c r="N46" s="22" t="n"/>
-      <c r="O46" s="22" t="n"/>
-      <c r="P46" s="22" t="n"/>
-      <c r="Q46" s="36">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
+      <c r="A46" s="42" t="n"/>
+      <c r="B46" s="42" t="n"/>
+      <c r="C46" s="42" t="n"/>
+      <c r="D46" s="42" t="n"/>
+      <c r="E46" s="42" t="n"/>
+      <c r="F46" s="42" t="n"/>
+      <c r="G46" s="42" t="n"/>
+      <c r="H46" s="42" t="n"/>
+      <c r="I46" s="42" t="n"/>
+      <c r="J46" s="42" t="n"/>
+      <c r="K46" s="42" t="n"/>
+      <c r="L46" s="42" t="n"/>
+      <c r="M46" s="42" t="n"/>
+      <c r="N46" s="42" t="n"/>
+      <c r="O46" s="42" t="n"/>
+      <c r="P46" s="42" t="n"/>
+      <c r="Q46" s="43" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="n"/>
-      <c r="B47" s="22" t="n"/>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="22" t="n"/>
-      <c r="F47" s="22" t="n"/>
-      <c r="G47" s="22" t="n"/>
-      <c r="H47" s="22" t="n"/>
-      <c r="I47" s="22" t="n"/>
-      <c r="J47" s="22" t="n"/>
-      <c r="K47" s="22" t="n"/>
-      <c r="L47" s="22" t="n"/>
-      <c r="M47" s="22" t="n"/>
-      <c r="N47" s="22" t="n"/>
-      <c r="O47" s="22" t="n"/>
-      <c r="P47" s="22" t="n"/>
-      <c r="Q47" s="36">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
+      <c r="A47" s="42" t="n"/>
+      <c r="B47" s="42" t="n"/>
+      <c r="C47" s="42" t="n"/>
+      <c r="D47" s="42" t="n"/>
+      <c r="E47" s="42" t="n"/>
+      <c r="F47" s="42" t="n"/>
+      <c r="G47" s="42" t="n"/>
+      <c r="H47" s="42" t="n"/>
+      <c r="I47" s="42" t="n"/>
+      <c r="J47" s="42" t="n"/>
+      <c r="K47" s="42" t="n"/>
+      <c r="L47" s="42" t="n"/>
+      <c r="M47" s="42" t="n"/>
+      <c r="N47" s="42" t="n"/>
+      <c r="O47" s="42" t="n"/>
+      <c r="P47" s="42" t="n"/>
+      <c r="Q47" s="43" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q47"/>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$7:$A$12</formula1>
     </dataValidation>
   </dataValidations>

--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -805,6 +805,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="41" t="inlineStr">
         <is>
@@ -1092,7 +1093,7 @@
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>پایین</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">

--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -710,7 +710,9 @@
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>هدف: اثبات اینکه تسک‌های CMSIS-RTOS2 ساده، خوانا، بدون HAL_Delay، با تخصیص استاتیک و zero کردن کامل snapshot کار می‌کنند</t>
+          <t>هدف: ثابت کنیم تسک‌های سیستم‌عامل (CMSIS-RTOS2) ساده و خوانا کار می‌کنند.
+تأخیر مستقیم (HAL_Delay) نداریم. حافظه فقط استاتیک است.
+عکس لحظه‌ای (snapshot) در هر تسک اول کامل صفر می‌شود.</t>
         </is>
       </c>
       <c r="B3" s="22" t="n"/>
@@ -726,7 +728,8 @@
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>قوانین: هر تست باید پیش‌شرط، ورودی، انتظار، معیار قبولی صریح داشته باشد؛ نتیجه واقعی فقط با اندازه‌گیری روی برد</t>
+          <t>قاعده: هر تست باید پیش‌شرط، ورودی، نتیجهٔ مورد انتظار و معیار قبولی روشن داشته باشد.
+نتیجهٔ واقعی فقط با اندازه‌گیری روی برد نوشته می‌شود.</t>
         </is>
       </c>
       <c r="B5" s="22" t="n"/>
@@ -757,7 +760,7 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
     </row>
@@ -774,7 +777,7 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>ایجاد اولیه Rtos_Validation — snapshot zeroing task_control (CO-023)، watchdog poll، ترتیب imbalance-&gt;fault-&gt;changeover-&gt;charger، static allocation</t>
+          <t>ساخته‌شدن اولیهٔ این فایل: صفرشدن عکس لحظه‌ای در تسک کنترل (تست CO-023)، چک‌کردن واچ‌داگ، ترتیب اجرا (اول عدم‌توازن، بعد خطا، بعد Changeover، بعد شارژر) و حافظهٔ استاتیک.</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -796,7 +799,7 @@
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>اضافه شدن RT-008..RT-010 برای panel dialog و Enter/Esc</t>
+          <t>تست‌های RT-008 تا RT-010 برای دیالوگ پنل و کلیدهای Enter و Esc اضافه شدند.</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -805,12 +808,15 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="41" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -964,7 +970,7 @@
       </c>
       <c r="I4" s="25" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="25" t="inlineStr">
@@ -989,12 +995,12 @@
       </c>
       <c r="N4" s="25" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="25" t="inlineStr">
@@ -2131,7 +2137,7 @@
       </c>
       <c r="I4" s="25" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="25" t="inlineStr">
@@ -2156,12 +2162,12 @@
       </c>
       <c r="N4" s="25" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="25" t="inlineStr">
@@ -2509,8 +2515,9 @@
         <is>
           <t>گام ۱: لینک و شارژر را فعال کن تا یک پاس واقعی control اجرا شود.
 گام ۲: یک پاس کامل task_control را با لاگ یا نقطه‌توقف (breakpoint) قدم‌به‌قدم دنبال کن.
-گام ۳: ترتیب اجرا باید دقیقاً این باشد: اول imbalance، بعد fault، بعد خطای فنی شارژر، بعد mcu_power_path، بعد changeover، بعد ارزیابی شارژر و در آخر poll واچ‌داگ.
-گام ۴: پاس باید در همان 10 میلی‌ثانیه تمام شود و ترتیب در همهٔ پاس‌ها حفظ شود.</t>
+گام ۳: ترتیب اجرا باید دقیقاً این باشد:
+اول عدم‌توازن (imbalance). بعد خطا (fault). بعد خطای فنی شارژر. بعد مسیر تغذیهٔ میکرو (mcu_power_path). بعد Changeover. بعد ارزیابی شارژر. در آخر چک واچ‌داگ (poll).
+گام ۴: پاس باید در همان 10 میلی‌ثانیه تمام شود و این ترتیب در همهٔ پاس‌ها حفظ شود.</t>
         </is>
       </c>
       <c r="F9" s="33" t="inlineStr">
@@ -3341,7 +3348,7 @@
       </c>
       <c r="H1" s="25" t="inlineStr">
         <is>
-          <t>commit رفع</t>
+          <t>نسخهٔ رفع</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -149,8 +149,14 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -187,6 +193,16 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -215,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -322,6 +338,28 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -692,7 +730,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Rtos — تسک‌ها، snapshot zeroing، watchdog، ترتیب اجرا</t>
         </is>
@@ -808,6 +846,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="41" t="inlineStr">
         <is>
@@ -859,7 +898,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Rtos</t>
         </is>
@@ -928,87 +967,87 @@
       <c r="Q3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="45" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="45" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="45" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="45" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr">
+      <c r="H4" s="45" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="45" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="25" t="inlineStr">
+      <c r="J4" s="45" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="45" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
+      <c r="L4" s="45" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="45" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="25" t="inlineStr">
+      <c r="N4" s="45" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="45" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="25" t="inlineStr">
+      <c r="P4" s="45" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="45" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -1092,48 +1131,48 @@
           <t>RT-009</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>panel dialog Enter/Esc</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>پنل باز و یک دیالوگ روی صفحه است</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="46" t="inlineStr">
         <is>
           <t>گام ۱: دیالوگ را با Enter تأیید کن و نتیجه را ببین.
 گام ۲: دوباره بازش کن و این بار با Esc ببند.</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="47" t="inlineStr">
         <is>
           <t>Enter و Esc روی دیالوگ پنل</t>
         </is>
       </c>
-      <c r="G6" s="33" t="inlineStr">
+      <c r="G6" s="47" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" s="46" t="inlineStr">
         <is>
           <t>Enter یعنی تأیید و Esc یعنی لغو؛ هر دو تمیز و بدون اثر اضافه کار می‌کنند</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="46" t="inlineStr">
         <is>
           <t>باید ببینید: هر دو کلید تمیز و بدون اثر اضافه کار می‌کنند؛ Enter تأیید و Esc لغو است. اگر برعکس یا بی‌اثر بودند، قبول نیست.</t>
         </is>
@@ -1146,13 +1185,13 @@
       </c>
       <c r="M6" s="32" t="n"/>
       <c r="N6" s="32" t="n"/>
-      <c r="O6" s="33" t="inlineStr">
+      <c r="O6" s="47" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P6" s="33" t="n"/>
-      <c r="Q6" s="35">
+      <c r="Q6" s="48">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -2003,7 +2042,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2030,7 +2069,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -2095,87 +2134,87 @@
       <c r="Q3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="45" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="45" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="45" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="45" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr">
+      <c r="H4" s="45" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="45" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="25" t="inlineStr">
+      <c r="J4" s="45" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="45" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
+      <c r="L4" s="45" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="45" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="25" t="inlineStr">
+      <c r="N4" s="45" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="45" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="25" t="inlineStr">
+      <c r="P4" s="45" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="45" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -2187,22 +2226,22 @@
           <t>RT-001</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>snapshot zeroing task_control</t>
         </is>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>برد با MODULE_MEASUREMENT=0 یا ADC نگه‌داشته</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>گام ۱: برد را با MODULE_MEASUREMENT=0 بوت کن (یا ADC را نگه دار تا snapshot نیاید).
 گام ۲: task_control را اجرا کن و snapshot را درست قبل از GetSnapshot بخوان.
@@ -2210,27 +2249,27 @@
 گام ۴: هیچ فیلدی نباید زبالهٔ پشته باشد؛ همین رفتار را در task_comm، task_ui و task_protection هم باید ببینی.</t>
         </is>
       </c>
-      <c r="F5" s="33" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G5" s="33" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>هر 9 فیلد snapshot صفر: v_in=0 v_bat24=0 v_bat12=0 v_low=0 v_high=0 i1=0 i2=0 input_present=false valid=false</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>امن</t>
         </is>
       </c>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="27" t="inlineStr">
         <is>
           <t>بدون زباله پشته؛ مانند task_comm/task_ui/task_protection</t>
         </is>
@@ -2242,18 +2281,18 @@
         </is>
       </c>
       <c r="M5" s="32" t="n"/>
-      <c r="N5" s="32" t="inlineStr">
+      <c r="N5" s="27" t="inlineStr">
         <is>
           <t>کد بازبینی + host test</t>
         </is>
       </c>
-      <c r="O5" s="33" t="inlineStr">
+      <c r="O5" s="29" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P5" s="33" t="n"/>
-      <c r="Q5" s="35" t="inlineStr">
+      <c r="Q5" s="31" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -2265,49 +2304,49 @@
           <t>RT-002</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>snapshot zeroing task_comm</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>برد با measurement خاموش</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="46" t="inlineStr">
         <is>
           <t>گام ۱: برد را با measurement خاموش بوت کن.
 گام ۲: task_comm را اجرا کن و snapshot را قبل از GetSnapshot بخوان (3 ثانیه).
 گام ۳: هر 9 فیلد باید از قبل صفر شده باشد؛ هیچ فیلد نامشخص (indeterminate) نباید در ساختار باشد.</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="F6" s="47" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="47" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H6" s="27" t="inlineStr">
+      <c r="H6" s="46" t="inlineStr">
         <is>
           <t>هر 9 فیلد صفر شده قبل از GetSnapshot</t>
         </is>
       </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="I6" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="J6" s="46" t="inlineStr">
         <is>
           <t>بدون indeterminate struct</t>
         </is>
@@ -2319,18 +2358,18 @@
         </is>
       </c>
       <c r="M6" s="27" t="n"/>
-      <c r="N6" s="27" t="inlineStr">
+      <c r="N6" s="46" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O6" s="29" t="inlineStr">
+      <c r="O6" s="47" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P6" s="29" t="n"/>
-      <c r="Q6" s="31" t="inlineStr">
+      <c r="Q6" s="48" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -2342,49 +2381,49 @@
           <t>RT-003</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>snapshot zeroing task_ui</t>
         </is>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>برد با measurement خاموش</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>گام ۱: برد را با measurement خاموش بوت کن.
 گام ۲: task_ui را اجرا کن (3 ثانیه).
 گام ۳: هر 9 فیلد snapshot باید صفر باشد و خروجی UI باید safe-off باشد؛ یعنی همهٔ LEDها خاموش بمانند.</t>
         </is>
       </c>
-      <c r="F7" s="33" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G7" s="33" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>هر 9 فیلد صفر؛ UI safe-off</t>
         </is>
       </c>
-      <c r="I7" s="32" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>safe-off</t>
         </is>
       </c>
-      <c r="J7" s="32" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>LED خاموش</t>
         </is>
@@ -2396,18 +2435,18 @@
         </is>
       </c>
       <c r="M7" s="32" t="n"/>
-      <c r="N7" s="32" t="inlineStr">
+      <c r="N7" s="27" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O7" s="33" t="inlineStr">
+      <c r="O7" s="29" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P7" s="33" t="n"/>
-      <c r="Q7" s="35" t="inlineStr">
+      <c r="Q7" s="31" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -2419,49 +2458,49 @@
           <t>RT-004</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>snapshot zeroing task_protection</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>برد با measurement خاموش</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="46" t="inlineStr">
         <is>
           <t>گام ۱: برد را با measurement خاموش بوت کن.
 گام ۲: task_protection را اجرا کن (3 ثانیه).
 گام ۳: هر 9 فیلد باید صفر باشد و Protection فقط valid را چک کند؛ هیچ fault کاذبی نباید ساخته شود.</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F8" s="47" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="G8" s="47" t="inlineStr">
         <is>
           <t>3s</t>
         </is>
       </c>
-      <c r="H8" s="27" t="inlineStr">
+      <c r="H8" s="46" t="inlineStr">
         <is>
           <t>هر 9 فیلد صفر؛ Protection فقط valid را چک کند</t>
         </is>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="J8" s="46" t="inlineStr">
         <is>
           <t>بدون fault کاذب</t>
         </is>
@@ -2473,18 +2512,18 @@
         </is>
       </c>
       <c r="M8" s="27" t="n"/>
-      <c r="N8" s="27" t="inlineStr">
+      <c r="N8" s="46" t="inlineStr">
         <is>
           <t>کد بازبینی</t>
         </is>
       </c>
-      <c r="O8" s="29" t="inlineStr">
+      <c r="O8" s="47" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P8" s="29" t="n"/>
-      <c r="Q8" s="31" t="inlineStr">
+      <c r="Q8" s="48" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -2496,22 +2535,22 @@
           <t>RT-005</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>ترتیب اجرا در task_control</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>لینک فعال + شارژر فعال</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>گام ۱: لینک و شارژر را فعال کن تا یک پاس واقعی control اجرا شود.
 گام ۲: یک پاس کامل task_control را با لاگ یا نقطه‌توقف (breakpoint) قدم‌به‌قدم دنبال کن.
@@ -2520,27 +2559,27 @@
 گام ۴: پاس باید در همان 10 میلی‌ثانیه تمام شود و این ترتیب در همهٔ پاس‌ها حفظ شود.</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="33" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t>10ms</t>
         </is>
       </c>
-      <c r="H9" s="32" t="inlineStr">
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>ترتیب ثابت: imbalance -&gt; fault -&gt; charger technical fault -&gt; mcu_power_path -&gt; changeover -&gt; charger evaluate -&gt; watchdog poll</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="32" t="inlineStr">
+      <c r="J9" s="27" t="inlineStr">
         <is>
           <t>ترتیب حفظ شود</t>
         </is>
@@ -2553,13 +2592,13 @@
       </c>
       <c r="M9" s="32" t="n"/>
       <c r="N9" s="32" t="n"/>
-      <c r="O9" s="33" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P9" s="33" t="n"/>
-      <c r="Q9" s="35" t="inlineStr">
+      <c r="Q9" s="31" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -2571,49 +2610,49 @@
           <t>RT-007</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>بدون HAL_Delay</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
         <is>
           <t>کد</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr">
+      <c r="E10" s="46" t="inlineStr">
         <is>
           <t>گام ۱: در کل پوشهٔ Firmware دنبال HAL_Delay بگرد (grep).
 گام ۲: باید صفر مورد پیدا شود.
 گام ۳: هر تأخیری در کد باید فقط از Rtos_DelayMilliseconds یا osDelayUntil باشد.</t>
         </is>
       </c>
-      <c r="F10" s="33" t="inlineStr">
+      <c r="F10" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="33" t="inlineStr">
+      <c r="G10" s="47" t="inlineStr">
         <is>
           <t>1s</t>
         </is>
       </c>
-      <c r="H10" s="32" t="inlineStr">
+      <c r="H10" s="46" t="inlineStr">
         <is>
           <t>هیچ HAL_Delay وجود نداشته باشد؛ فقط Rtos_DelayMilliseconds و osDelayUntil</t>
         </is>
       </c>
-      <c r="I10" s="32" t="inlineStr">
+      <c r="I10" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="32" t="inlineStr">
+      <c r="J10" s="46" t="inlineStr">
         <is>
           <t>0 مورد HAL_Delay</t>
         </is>
@@ -2625,18 +2664,18 @@
         </is>
       </c>
       <c r="M10" s="32" t="n"/>
-      <c r="N10" s="32" t="inlineStr">
+      <c r="N10" s="46" t="inlineStr">
         <is>
           <t>check_ai_rules.sh</t>
         </is>
       </c>
-      <c r="O10" s="33" t="inlineStr">
+      <c r="O10" s="47" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P10" s="33" t="n"/>
-      <c r="Q10" s="35" t="inlineStr">
+      <c r="Q10" s="48" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -2726,22 +2765,22 @@
           <t>RT-011</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t>تبدیل تیک به ms در چک‌این‌های IWDG</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="D12" s="46" t="inlineStr">
         <is>
           <t>کد</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="46" t="inlineStr">
         <is>
           <t>گام ۱: هر 7 محل check-in و poll واچ‌داگ را در پنج تسک پیدا کن (task_control، task_comm، task_measurement، task_protection و task_ui).
 گام ۲: در هر محل چک کن زمان از تبدیل func__Rtos_TicksToMilliseconds(osKernelGetTickCount()) گذشته باشد، نه تیک خام کرنل.
@@ -2749,32 +2788,32 @@
 گام ۴ (برد): روی برد واقعی واچ‌داگ را زیر نظر بگیر؛ اگر روزی فرکانس تیک عوض شود، مهلت‌ها خودکار بر حسب میلی‌ثانیه درست می‌مانند. تست برد هنوز در انتظار است.</t>
         </is>
       </c>
-      <c r="F12" s="33" t="inlineStr">
+      <c r="F12" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="33" t="inlineStr">
+      <c r="G12" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="32" t="inlineStr">
+      <c r="H12" s="46" t="inlineStr">
         <is>
           <t>در فرکانس تیک ۱۰۰۰ هرتز رفتار دقیقاً مثل قبل؛ اگر روزی فرکانس تیک عوض شود، مهلت‌های واچ‌داگ خودکار بر حسب ms درست می‌مانند</t>
         </is>
       </c>
-      <c r="I12" s="32" t="inlineStr">
+      <c r="I12" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="32" t="inlineStr">
+      <c r="J12" s="46" t="inlineStr">
         <is>
           <t>هیچ چک‌اینی تیک خام را جای ms ندهد؛ هر دو گیت سبز</t>
         </is>
       </c>
-      <c r="K12" s="32" t="inlineStr">
+      <c r="K12" s="46" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: هر دو گیت سبز، بودجهٔ RAM/فلش بدون تغییر؛ تست برد: در انتظار</t>
         </is>
@@ -2786,13 +2825,13 @@
       </c>
       <c r="M12" s="32" t="n"/>
       <c r="N12" s="32" t="n"/>
-      <c r="O12" s="33" t="inlineStr">
+      <c r="O12" s="47" t="inlineStr">
         <is>
           <t>004fbf1</t>
         </is>
       </c>
       <c r="P12" s="33" t="n"/>
-      <c r="Q12" s="35" t="inlineStr">
+      <c r="Q12" s="48" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
@@ -3257,11 +3296,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>مرجع سناریوهای Rtos</t>
         </is>
@@ -3295,6 +3334,8 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3311,84 +3352,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>شناسه ایراد</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="F1" s="25" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>تاریخ ثبت</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>تاریخ رفع</t>
         </is>
       </c>
-      <c r="H1" s="25" t="inlineStr">
+      <c r="H1" s="45" t="inlineStr">
         <is>
           <t>نسخهٔ رفع</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>BUG-RT-001</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="52" t="inlineStr">
         <is>
           <t>RT-001</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="53" t="inlineStr">
         <is>
           <t>task_control فقط valid=false می‌کرد، 8 فیلد دیگر زباله پشته داشت — latent defect</t>
         </is>
       </c>
-      <c r="D2" s="21" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="53" t="inlineStr">
         <is>
           <t>رفع شد</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="53" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="G2" s="21" t="inlineStr">
+      <c r="G2" s="53" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="H2" s="21" t="inlineStr">
+      <c r="H2" s="53" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
@@ -3410,11 +3451,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Rtos</t>
         </is>
@@ -3440,6 +3481,8 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3448,7 +3491,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3456,7 +3499,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>فهرست ثابت‌ها و آستانه‌های Rtos</t>
         </is>
@@ -3551,11 +3594,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>ماشین حالت Rtos — تسک‌ها</t>
         </is>
@@ -3596,6 +3639,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Rtos/Rtos_Validation.xlsx
+++ b/Firmware/Modules/Rtos/Rtos_Validation.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -155,6 +155,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -231,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -360,6 +365,15 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -726,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,7 +860,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="41" t="inlineStr">
         <is>
@@ -856,6 +869,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="54" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -875,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -895,6 +920,7 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1052,6 +1078,11 @@
           <t>تاریخ</t>
         </is>
       </c>
+      <c r="R4" s="45" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="54" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
@@ -1124,6 +1155,11 @@
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
+      <c r="R5" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
@@ -1195,6 +1231,11 @@
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
+      <c r="R6" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
@@ -1265,6 +1306,11 @@
       <c r="Q7" s="31">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
+      </c>
+      <c r="R7" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3296,7 +3342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3334,8 +3380,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3451,7 +3495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3481,8 +3525,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3594,7 +3636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3639,7 +3681,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
